--- a/data/Bang_Tham_Dinh_Du_Toan.xlsx
+++ b/data/Bang_Tham_Dinh_Du_Toan.xlsx
@@ -103,13 +103,13 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,28 +476,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M102"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="38" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Mau_Du_Toan_Tham_Dinh (2)</t>
+          <t>Bang_Tham_Dinh_Du_Toan (3) - Bản Mới</t>
         </is>
       </c>
     </row>
@@ -521,57 +524,72 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Tên Quy Cách Kỹ Thuật</t>
+          <t>Tên Vật Tư</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
+          <t>Thông Số Kỹ Thuật</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>HSX/XX (Trình)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
           <t>ĐVT</t>
         </is>
       </c>
-      <c r="E4" s="1" t="inlineStr">
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>Số Lượng</t>
         </is>
       </c>
-      <c r="F4" s="1" t="inlineStr">
+      <c r="H4" s="1" t="inlineStr">
         <is>
           <t>Đơn Giá Đề Nghị (Trình)</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
+      <c r="I4" s="1" t="inlineStr">
         <is>
           <t>Thành Tiền Đề Nghị</t>
         </is>
       </c>
-      <c r="H4" s="1" t="inlineStr">
+      <c r="J4" s="1" t="inlineStr">
         <is>
           <t>ĐÁNH GIÁ CỦA TỔ THẨM ĐỊNH (TTĐ)</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Ý KIẾN PHẢN BIỆN CỦA PHÒNG KHVT</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Đơn Giá Thống Nhất</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Thành Tiền Thống Nhất</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Giá Trị Giảm</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>Cơ Sở Thống Nhất</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>Ghi Chú</t>
         </is>
       </c>
     </row>
@@ -584,39 +602,73 @@
           <t>3.82.63.134.ENG.00.000</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Module đầu vào input IUX 760 MI - Điện áp hoạt động: 17-28VDC
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Module đầu vào input IUX 760 MI</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Điện áp hoạt động: 17-28VDC
 Partno: 908531
 Hãng sản xuất: Minimax</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Minimax/ Đức</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="G5" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <v>13559000</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="I5" s="7" t="n">
         <v>54236000</v>
       </c>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="6" t="n">
-        <v>13559000</v>
-      </c>
-      <c r="K5" s="6" t="n">
-        <v>54236000</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>TỔ THẨM ĐỊNH NHÀ MÁY NHIỆT ĐIỆN VĨNH TÂN 4
+TỔ THẨM ĐỊNH DỰ TOÁN
+BÁO CÁO THUYẾT MINH THẨM ĐỊNH ĐƠN GIÁ VẬT TƯ
+Đơn vị yêu cầu: NMNĐ Vĩnh Tân 4
+Mã ERP: 3.82.63.134.ENG.00.000 | Số lượng: 4 Cái
+Tên vật tư: Module đầu vào input IUX 760 MI – Điện áp hoạt động: 17-28VDC
+Partno: 908531 | Hãng sản xuất: Minimax
+Đơn giá trình thẩm định: 13.559.000 đ/Cái
+1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định tiến hành đối chiếu đơn giá trình thẩm định đối với mặt hàng Module đầu vào input IUX 760 MI (Partno: 908531, hãng Minimax) trên 5 cơ sở chứng cứ thu thập được, cụ thể:
+(1) Báo giá gốc thương mại; (2) Lịch sử mua sắm trên ERP Vĩnh Tân 4; (3) Cơ sở dữ liệu mua sắm EVN IMIS của các Đơn vị Phát điện trong Tập đoàn; (4) Cơ sở dữ liệu Mua sắm Công (e-GP); (5) Khảo sát giá thương mại điện tử trên các sàn giao dịch và Internet.
+Kết quả tổng hợp cho thấy đơn giá trình 13.559.000 đ/Cái là mức chào thấp nhất từ nhà thầu trong báo giá thương mại hiện tại; tuy nhiên khi đối chiếu với lị</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr"/>
+      <c r="L5" s="7" t="n">
+        <v>6015000</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>24060000</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>30176000</v>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>Ý kiến Chuyên gia AI &amp; Báo giá thấp nhất DTL (Khối 1)</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>3.82.63.134.ENG.00.000 | Khắc phục tồn tại thiết bị | BBKT 23/2026/PXH-VT4. Vật tư không có trong KH SXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -627,37 +679,61 @@
           <t>3.34.40.024.ENG.00.000</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953 - Nút nhấn khẩn cấp, Part no: 58100-953, Nguồn cấp: 17 - 28VDC , IP67. NSX: Apollo</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Nút nhấn khẩn cấp, Part no: 58100-953, Nguồn cấp: 17 - 28VDC , IP67. NSX: Apollo</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Apollo/ Anh</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="G6" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="H6" s="7" t="n">
         <v>14208000</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="I6" s="7" t="n">
         <v>14208000</v>
       </c>
-      <c r="H6" s="7" t="inlineStr"/>
-      <c r="I6" s="7" t="inlineStr"/>
-      <c r="J6" s="6" t="n">
-        <v>14208000</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>14208000</v>
-      </c>
-      <c r="L6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+Căn cứ tính chất kỹ thuật, thương hiệu sản xuất và chứng cứ thu thập tại 05 cơ sở thẩm định, Tổ Thẩm định dự toán – Nhà máy Nhiệt điện Vĩnh Tân 4 thống nhất nội dung đánh giá đối với vật tư: Nút nhấn khẩn cấp Discovery Manual Call Point, Part no: 58100-953, nguồn cấp 17 – 28VDC, cấp bảo vệ IP67, nhà sản xuất Apollo (Mã ERP: 3.34.40.024.ENG.00.000), số lượng 01 cái, đơn giá trình thẩm định 14.208.000 đ</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr"/>
+      <c r="L6" s="7" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>7208000</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (QĐ 161)</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>3.34.40.024.ENG.00.000 | Khắc phục tồn tại thiết bị | BBKT 23/2026/PXH-VT4. Vật tư không có trong KH SXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -668,9 +744,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Actuator khí nén FlowTek Series 92 - Actuator khí nén:
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Actuator khí nén FlowTek Series 92</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Actuator khí nén:
 Model:
  FlowTek Series 92 (920830-113A0532)
 Type: DOUBLE ACTING
@@ -680,32 +761,57 @@
 Nhà sản xuất: Bray International</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Bray/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="G7" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="H7" s="7" t="n">
         <v>56000000</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="I7" s="7" t="n">
         <v>280000000</v>
       </c>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="6" t="n">
-        <v>56000000</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>280000000</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7" t="inlineStr"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Actuator khí nén FlowTek Series 92 (Double Acting) - Model: 920830-113A0532.
+• Đơn giá trình thẩm định: 56.000.000 VNĐ/Bộ (Số lượng: 5 Bộ).
+• Đánh giá Chứng cứ Thẩm định: Đạt 80/100 điểm (4/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: Đơn giá trình cao hơn so với mốc giá tham chiếu TMĐT có phụ thu nhập cảnh Landed Cost.
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Báo giá chào hợp lệ là 56.000.000 VNĐ/Bộ từ Nhà thầu chào (khớp 100% với đơn giá trình).
+- Cơ sở 2 (ERP Vĩnh Tân 4): CSDL ERP nội bộ chưa ghi nhận mã vật tư tương đương.
+- Cơ sở 3 (EVN IMIS): Chưa có dữ liệu mua sắm tương đương trên CSDL EVN IMIS toà</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr"/>
+      <c r="L7" s="7" t="n">
+        <v>16491600</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>82458000</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>197542000</v>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 5: Tham khảo TMĐT / Giá Web (Landed Cost DDP VT4)</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Khắc phục tồn tại thiết bị | BBKT 547/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -716,9 +822,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Solenoid van 600250-70900533 - Solenoid van:
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Solenoid van 600250-70900533</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Solenoid van:
 Mã thiết bị: 600250-70900533
 Loại van: Van điều khiển ống dẫn (spool control valve) được vận hành bằng khí nén (pilot-operated).
 Điện áp: 24 VAC.
@@ -729,32 +840,52 @@
 Nhà sản xuất: Bray International.</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Bray/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="G8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="H8" s="7" t="n">
         <v>64000000</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="I8" s="7" t="n">
         <v>320000000</v>
       </c>
-      <c r="H8" s="7" t="inlineStr"/>
-      <c r="I8" s="7" t="inlineStr"/>
-      <c r="J8" s="6" t="n">
-        <v>64000000</v>
-      </c>
-      <c r="K8" s="6" t="n">
-        <v>320000000</v>
-      </c>
-      <c r="L8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7" t="inlineStr"/>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t># THUYẾT MINH THẨM ĐỊNH MỤC STT 4
+## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+Tổ Thẩm định thực hiện thẩm định đánh giá sau cùng đối với vật tư Solenoid van 600250-70900533 (Hãng SX: Bray International, số lượng 5 Bộ). Đơn giá dự toán trình là 64.000.000 đ/Bộ, cao hơn +610.4% so với đơn giá tham chiếu thấp nhất hợp lệ (9.009.300 đ từ Cơ sở 5). Tổ Thẩm định đề xuất điều chỉnh đơn giá theo giá thị trường quốc tế đã tính đủ chi phí nhập cảnh &amp; vận chuyển DDP Vĩ</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr"/>
+      <c r="L8" s="7" t="n">
+        <v>9009300</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>45046500</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>274953500</v>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 5: Tham khảo TMĐT / Giá Web</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Khắc phục tồn tại thiết bị | BBKT 547/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -765,37 +896,70 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Spiral Wound Gasket DN200 PN40 - Spiral Wound Gasket DN200 PN40 RF – EN 1514-2 – Type CGI – SS316L/PTFE/SS316L/CS</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Spiral Wound Gasket DN200 PN40</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Spiral Wound Gasket DN200 PN40 RF – EN 1514-2 – Type CGI – SS316L/PTFE/SS316L/CS</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>QT/ Việt Nam</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="G9" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="H9" s="7" t="n">
         <v>1500000</v>
       </c>
-      <c r="G9" s="6" t="n">
+      <c r="I9" s="7" t="n">
         <v>3000000</v>
       </c>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="6" t="n">
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Spiral Wound Gasket DN200 PN40 (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 1.500.000 VNĐ (Số lượng: 2 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 80/100 điểm (Hạng A - 4/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.500.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 1 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL Kế toán ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Spiral Wound Gasket DN200 PN40], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Spiral Wound Gasket DN200 PN40] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Spiral Wound Gasket] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Spiral Wound Gasket DN200 PN40] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.500.000 VNĐ/Cái.</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr"/>
+      <c r="L9" s="7" t="n">
         <v>1500000</v>
       </c>
-      <c r="K9" s="6" t="n">
+      <c r="M9" s="7" t="n">
         <v>3000000</v>
       </c>
-      <c r="L9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="7" t="inlineStr"/>
+      <c r="N9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay mới van tổng cấp bồn CO2 bị rò qua van và ty van | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -806,37 +970,66 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>GEFA DG1 Ball Valve - GEFA DG1 Ball Valve, DN50/65, PN125, Body SS316 (1.4408), High Pressure Ball Valve, Rohrgewinde DIN 2999-Rp, ISO 228/1-G</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>GEFA DG1 Ball Valve</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>GEFA DG1 Ball Valve, DN50/65, PN125, Body SS316 (1.4408), High Pressure Ball Valve, Rohrgewinde DIN 2999-Rp, ISO 228/1-G</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Gefa-xx/ Đức</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="G10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="H10" s="7" t="n">
         <v>61250000</v>
       </c>
-      <c r="G10" s="6" t="n">
+      <c r="I10" s="7" t="n">
         <v>61250000</v>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
-      <c r="I10" s="7" t="inlineStr"/>
-      <c r="J10" s="6" t="n">
-        <v>61250000</v>
-      </c>
-      <c r="K10" s="6" t="n">
-        <v>61250000</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7" t="inlineStr"/>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 61.250.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 21.100.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:182) theo hóa đơn số 0000198 ngày 08.07.2020 ngày 2020-10-29. SL: 3 Cái); Các đợt nhập khác: 51.118.100 đ, 58.245.912 đ
+• Cơ sở 3 (EVN IMIS): IMIS EVN: 8.910.000 đ/Cái (Công ty Nhiệt điện Duyên Hải)
+• Cơ sở 4 (Mua Sắm Công e-GP): Chưa có dữ liệu Mua sắm công e-GP
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 8.910.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr"/>
+      <c r="L10" s="7" t="n">
+        <v>8910000</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>8910000</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>52340000</v>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay mới van bypass đầu ra bồn CO2 DN50 bị rò qua ty van và đoạn ống kết nối bị rò rỉ tại vị trí ren | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -847,9 +1040,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Selector valve KMX CO2 - Selector valve KMX CO₂ LP piston controlled, complete
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Selector valve KMX CO2</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Selector valve KMX CO₂ LP piston controlled, complete
 - Size: DN50
 ­	End Connection: Flange DIN 2501 PN40
 ­	Working pressure: 25 bar
@@ -857,32 +1055,56 @@
 ­	Housing: Cast steel, Piston: GJL-250, Piston Rod: AISI 303</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Minimax/ Đức</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="G11" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="H11" s="7" t="n">
         <v>452147000</v>
       </c>
-      <c r="G11" s="6" t="n">
+      <c r="I11" s="7" t="n">
         <v>452147000</v>
       </c>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="6" t="n">
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 135.000.000 đ/Cái (CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 4.925.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:136/2021) theo hóa đơn số 57 ngày 26.01.2022 ngày 2022-01-26. SL: 1 Cái); Các đợt nhập khác: 3.910.000 đ
+• Cơ sở 3 (EVN IMIS): Chưa có dữ liệu EVN IMIS
+• Cơ sở 4 (Mua Sắm Công e-GP): Chưa có dữ liệu Mua sắm công e-GP
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 4.925.000 đ/Cái.</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr"/>
+      <c r="L11" s="7" t="n">
         <v>452147000</v>
       </c>
-      <c r="K11" s="6" t="n">
+      <c r="M11" s="7" t="n">
         <v>452147000</v>
       </c>
-      <c r="L11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
+        </is>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay mới van chính đầu ra bồn CO2 DN50 bị rò qua van và ty van | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -893,9 +1115,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Union G 10-PL A3C - Union 
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Union G 10-PL A3C</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Union 
 - Type: G - Union 
 - Model: G 10-PL A3C 
 - Part no.: 125943 
@@ -906,32 +1133,54 @@
 - Manufacturer: Minimax Gmb, Germany</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Minimax/ Đức</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="G12" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="H12" s="7" t="n">
         <v>1004000</v>
       </c>
-      <c r="G12" s="6" t="n">
+      <c r="I12" s="7" t="n">
         <v>10040000</v>
       </c>
-      <c r="H12" s="7" t="inlineStr"/>
-      <c r="I12" s="7" t="inlineStr"/>
-      <c r="J12" s="6" t="n">
-        <v>1004000</v>
-      </c>
-      <c r="K12" s="6" t="n">
-        <v>10040000</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="7" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 1.004.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 620.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ:03/2022) theo hóa đơn số 00000024 ngày 01.04.2022 ngày Đầu. SL: 6 Cái); Các đợt nhập khác: 18.374.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [125943], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắ</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr"/>
+      <c r="L12" s="7" t="n">
+        <v>620000</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>3840000</v>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: Lịch sử mua sắm ERP Vĩnh Tân 4 (HĐ 03/2022)</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay mới các đầu nối, đường ống điều khiển khí nén các van actuator phun CO2 bị rò rỉ và gỉ sét | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -942,9 +1191,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Elbow union - Elbow union 
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Elbow union</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Elbow union 
 - Type: W - Elbow union 
 - Model: W 10-PL A3C
 - Part no.: 174678 
@@ -955,32 +1209,58 @@
 - Manufacturer: Minimax Gmb, Germany</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Minimax/ Đức</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="G13" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="H13" s="7" t="n">
         <v>1315000</v>
       </c>
-      <c r="G13" s="6" t="n">
+      <c r="I13" s="7" t="n">
         <v>6575000</v>
       </c>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="6" t="n">
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Elbow union (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 1.315.000 VNĐ (Số lượng: 5 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.315.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 2 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL Kế toán ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Elbow union], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [10-PL A3C] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [W 10-PL A3C] trên Cổng Mạng Đấu thầu Quố</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr"/>
+      <c r="L13" s="7" t="n">
         <v>1315000</v>
       </c>
-      <c r="K13" s="6" t="n">
+      <c r="M13" s="7" t="n">
         <v>6575000</v>
       </c>
-      <c r="L13" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
+        </is>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay mới các đầu nối, đường ống điều khiển khí nén các van actuator phun CO2 bị rò rỉ và gỉ sét | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -991,9 +1271,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Union tee - Union tee 
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Union tee</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Union tee 
 - Type: T - Union tee 
 - Model: T - PL A3C 
 - Part no.: 125645 
@@ -1004,32 +1289,81 @@
 - Manufacturer: Minimax Gmb, Germany</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Minimax/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n">
+      <c r="G14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="H14" s="7" t="n">
         <v>1508000</v>
       </c>
-      <c r="G14" s="6" t="n">
+      <c r="I14" s="7" t="n">
         <v>7540000</v>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
-      <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="6" t="n">
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>I. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
+| Hạng mục | Nội dung |
+|---|---|
+| Tên vật tư | Union tee (Type: T - Union tee, Model: T - PL A3C, Part no.: 125645) kèm Progressive ring DPR 10-L/S A3D (Part no.: 126091) lắp đặt tại ba đầu, Pipe OD 10 mm |
+| Hãng sản xuất / Xuất xứ | Minimax GmbH – Germany (tiêu chuẩn kỹ thuật an toàn Châu Âu, nhóm G7) |
+| Mã ERP nội bộ | Chưa có mã vật tư |
+| Số lượng | 05 Cái |
+| Đơn giá trình thẩm định | 1.508.000 đ/Cái |
+| Thành tiền trình | 7.540.000 đ |
+| Đơn giá tham chiếu thấp nhất hợp lệ | 836.800 đ/Cái |
+| Mức chênh lệch | +80,2% so với đơn giá trình |
+| Tiết kiệm dự kiến (nếu điều chỉnh) | 3.356.000 đ |
+II. 🔍 Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
+**1. Phân tích bản chất kỹ thuật vật tư**
+Vật tư thẩm định là cụm chi tiết kết nối thuộc hệ thống đường ống thủy lực/khí nén công nghiệp, gồm Union tee Model T - PL A3C (Part no. 125645) kích thước Pipe OD 10 mm kèm bộ ba Progressive ring DPR 10-L/S A3D (Part no. 126091) lắp đặt tại cả ba đầu nối. Đây là vật tư chuyên dụng của hãng Minimax GmbH (Đức) – thương hiệu thuộc nhóm tiêu chuẩn kỹ thuật an toàn cao Châu Âu/G7, có yêu cầu nghiêm ngặt về độ kín khít, áp suất làm việc, khả năng chịu rung và độ bền mỏi trong điều kiện vận hành liên tục tại Nhà máy Nhiệt điện Vĩnh Tân 4. Tính đặc thù của vật tư thể hiện ở chỗ: cụm Union tee và Progressive ring phải đồng bộ chủng loại, kích thước, vật liệu và xuất xứ để đảm bảo độ tương thích ren – vòng đệt tiến tiến (progressive ring), qua đó duy trì áp suất danh định và độ tin cậy của hệ thống. Tổ Thẩm định xếp vật tư vào phân nhóm **Thiết bị công nghiệp chuyên dụng – linh kiện kết nối có yêu cầu kỹ thuật đặc thù**.
+**2. Đánh giá tương quan giá trị kỹ thuật và thương mại**
+Đơn giá trình thẩm định 1.508.000 đ/Cái cao hơn **+80,2%** so với đơn giá tham chiếu thấp nhất hợp lệ là 836.800 đ/Cái (mức chênh tuyệt đối 671.200 đ/Cái). Với đặc tính kỹ thuật của cụm vật tư chuyên dụng G7, biên độ chênh lệch này vượt khá xa ngưỡng biến động hợp lý thường gặp (thông thường dưới 15–20%) giữa các báo giá cùng chủng loại, cùng xuất xứ. Tổ Thẩm định nhận thấy mức giá trình chưa có cơ sở thuyết phục để chứng minh tính hợp lý và cần được đàm phán điều chỉnh về mặt bằng giá thị trường.
+**3. Đối chiếu 05 cơ sở chứng cứ thẩm định**
+- **Cơ sở 1 – Báo giá gốc (thương mại):** Tổ Thẩm định đã đối chiếu các báo giá thương mại thu thập được; mức chào thấp nhất hợp lệ là **836.800 đ/Cái** từ Nhà thầu chào giá cạnh tranh. Đơn giá trình 1.508.000 đ/Cái không phải mức thấp nhất trên thị trường, chênh lệch +80,2% cho thấy dấu hiệu bất thường cần đàm phán.
+- **Cơ sở 2 – Cơ sở dữ liệu ERP Nhà máy Nhiệt điện Vĩnh Tân 4:** Qua rà soát CSDL Kế toán ERP, không có kết quả tra cứu nào có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Tổ Thẩm định **không áp dụng** CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- **Cơ sở 3 – Cơ sở dữ liệu EVN IMIS:** Tra cứu theo từ khóa **[DPR 10-L/S]** cho thấy các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán. Tổ Thẩm định **không áp dụng** làm căn cứ thẩm định.
+- **Cơ sở 4 – Hệ thống Mua sắm Công (e-GP) – muasamcong.mpi.gov.vn:** Tra cứu từ khóa **[126091]** tại thời điểm 18:31 ngày 07/09/2026 **chưa ghi nhận** kết quả trúng thầu tương tự. Tổ Thẩm định ghi nhận sự hạn chế dữ liệu tham chiếu từ kênh này.
+- **Cơ sở 5 – Thương mại điện tử:** Dữ liệu không khả dụng/không có kết quả phù hợp để đối chiếu; Tổ Thẩm định **không áp dụng** làm căn cứ so sánh đơn giá.
+**4. Nhận định chung**
+Trong 05 cơ sở chứng cứ, chỉ có Cơ sở 1 (Báo giá gốc thương mại) cung cấp được mức giá hợp lệ để đối chiếu; các cơ sở còn lại đều không có dữ liệu tương đồng phù hợp hoặc không khả dụng. Tổ Thẩm định lấy mức chào thấp nhất hợp lệ 836.800 đ/Cái làm đơn giá tham chiếu phê duyệt, đồng thời cảnh báo bất thường đơn giá trình thẩm định.
+III. 💡 KẾT LUẬN &amp; ĐỀ XUẤT PHÊ DUYỆT CỦA TỔ THẨM ĐỊNH TRÌNH LÃNH ĐẠO
+🔴 **CẢNH BÁO BẤT THƯỜNG ĐƠN GIÁ:** Đơn giá trình 1.508.000 đ/Cái chênh lệch **+80,2%** so với đơn giá tham chiếu thấp nhất hợp lệ, vượt ngưỡng biên độ an toàn kỹ thuật – thương mại cho vật tư chuyên dụng G7. Tổ Thẩm định đề xuất Lãnh đạo/Hội đồng Thẩm định **đàm phán điều chỉnh đơn giá phê duyệt về mức 836.800 đ/Cái**, tương ứng thành tiền **4.184.000 đ** cho 05 Cái, **dự kiến tiết kiệm 3.356.000 đ** cho Nhà máy Nhiệt điện Vĩnh Tân 4.
+Trường hợp Nhà thầu không chấp thuận điều chỉnh về mức 836.800 đ/Cái, Tổ Thẩm định đề xuất:
+- Yêu cầu Nhà thầu cung cấp **hóa đơn/chứng từ mua hàng trước đó** hoặc **báo giá từ hãng Minimax GmbH** để chứng minh tính hợp lý của mức giá 1.508.000 đ/Cái;
+- Xem xét mời thêm tối thiểu 02 Nhà thầu có năng lực cung cấp vật tư tương đương để tổ chức đàm phán cạnh tranh trước khi trình phê duyệt;
+- Báo cáo Lãnh đạo quyết định phương án tối ưu trên nguyên tắc đảm bảo yêu cầu kỹ thuật, tiến độ và hiệu quả chi phí.
+Tổ Thẩm định kính trình Lãnh đạo/Hội đồng Thẩm định xem xét, quyết định.</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr"/>
+      <c r="L14" s="7" t="n">
         <v>1508000</v>
       </c>
-      <c r="K14" s="6" t="n">
+      <c r="M14" s="7" t="n">
         <v>7540000</v>
       </c>
-      <c r="L14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7" t="inlineStr"/>
+      <c r="N14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay mới các đầu nối, đường ống điều khiển khí nén các van actuator phun CO2 bị rò rỉ và gỉ sét | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1040,41 +1374,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Ống B-210-2394/1 - Tube 
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Ống B-210-2394/1</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Tube 
 - Model: B-210-2394/1 
 - OD: 10mm (DN8) 
 - Part no.: 823575
 - Test pressure: 210 (bar)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Minimax/ Đức</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n">
+      <c r="G15" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="H15" s="7" t="n">
         <v>1205000</v>
       </c>
-      <c r="G15" s="6" t="n">
+      <c r="I15" s="7" t="n">
         <v>24100000</v>
       </c>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="6" t="n">
+      <c r="J15" s="6" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr"/>
+      <c r="L15" s="7" t="n">
         <v>1205000</v>
       </c>
-      <c r="K15" s="6" t="n">
+      <c r="M15" s="7" t="n">
         <v>24100000</v>
       </c>
-      <c r="L15" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="6" t="inlineStr"/>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay mới các đầu nối, đường ống điều khiển khí nén các van actuator phun CO2 bị rò rỉ và gỉ sét | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1085,9 +1434,14 @@
           <t>3.96.13.021.GER.00.000</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T - Cảm biến đo khối lượng (Loadcell):
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến đo khối lượng (Loadcell):
 - Model: RTNC3/10T
 - Odering number: K-RTN-8-C3-10-N-12-N-N-8
 - Maximum capacity (Emax): 10000kg
@@ -1106,32 +1460,42 @@
 - Manufacturer: Hottinger Baldwin Messtechnik GmbH (HBM), Germany</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>HBK/ Đức</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n">
+      <c r="G16" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="H16" s="7" t="n">
         <v>117600000</v>
       </c>
-      <c r="G16" s="6" t="n">
+      <c r="I16" s="7" t="n">
         <v>117600000</v>
       </c>
-      <c r="H16" s="7" t="inlineStr"/>
-      <c r="I16" s="7" t="inlineStr"/>
-      <c r="J16" s="6" t="n">
+      <c r="J16" s="6" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr"/>
+      <c r="L16" s="7" t="n">
         <v>117600000</v>
       </c>
-      <c r="K16" s="6" t="n">
+      <c r="M16" s="7" t="n">
         <v>117600000</v>
       </c>
-      <c r="L16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>3.96.13.021.GER.00.000 | Thay thế 01 cảm biến đo khối lượng (Loadcell) bồn chứa khí CO2 – Tổ máy S3 bị hư hỏng | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -1142,9 +1506,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-AH400. Type G1, 65kW, TS250H - MCC bucket 
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-AH400. Type G1, 65kW, TS250H</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>MCC bucket 
 - MCC unit order code: P0BHC01GH004R-A H400
 - Type: G1
 - Load description: Spare
@@ -1161,32 +1530,42 @@
 - Manufacturer: LS Electric, Korea</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>LS/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="G17" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="H17" s="7" t="n">
         <v>284390000</v>
       </c>
-      <c r="G17" s="6" t="n">
+      <c r="I17" s="7" t="n">
         <v>284390000</v>
       </c>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="6" t="n">
+      <c r="J17" s="6" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr"/>
+      <c r="L17" s="7" t="n">
         <v>284390000</v>
       </c>
-      <c r="K17" s="6" t="n">
+      <c r="M17" s="7" t="n">
         <v>284390000</v>
       </c>
-      <c r="L17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="7" t="inlineStr"/>
+      <c r="N17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Khắc phục theo BBKT 1002/2026/VH-VT4 | Vật tư mua mới, chưa đề xuất trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -1197,9 +1576,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-BH200. Type S - MCC bucket 
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-BH200. Type S</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>MCC bucket 
 - MCC unit order code: P0BHC01GH004R-B H200
 - Load description: Space
 - Type: S
@@ -1207,32 +1591,42 @@
 - Manufacturer: LS Electric, Korea</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>LS/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n">
+      <c r="G18" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="6" t="n">
+      <c r="H18" s="7" t="n">
         <v>183501000</v>
       </c>
-      <c r="G18" s="6" t="n">
+      <c r="I18" s="7" t="n">
         <v>183501000</v>
       </c>
-      <c r="H18" s="7" t="inlineStr"/>
-      <c r="I18" s="7" t="inlineStr"/>
-      <c r="J18" s="6" t="n">
+      <c r="J18" s="6" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="7" t="n">
         <v>183501000</v>
       </c>
-      <c r="K18" s="6" t="n">
+      <c r="M18" s="7" t="n">
         <v>183501000</v>
       </c>
-      <c r="L18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7" t="inlineStr"/>
+      <c r="N18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Khắc phục theo BBKT 1002/2026/VH-VT4 | Vật tư mua mới, chưa đề xuất trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -1243,9 +1637,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-CH200. Type G1, 8.1kW, TS100H - MCC bucket 
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Tủ MCC bucket - MCC unit order code: P0BHC01GH004R-CH200. Type G1, 8.1kW, TS100H</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>MCC bucket 
 - MCC unit order code: P0BHC01GH004R-C H200
 - Load description: Spare
 - Capacity: 8.1kW
@@ -1261,32 +1660,42 @@
 - Manufacturer: LS Electric, Korea</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>LS/ Việt Nam</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n">
+      <c r="G19" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="H19" s="7" t="n">
         <v>233654000</v>
       </c>
-      <c r="G19" s="6" t="n">
+      <c r="I19" s="7" t="n">
         <v>233654000</v>
       </c>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="6" t="n">
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr"/>
+      <c r="L19" s="7" t="n">
         <v>233654000</v>
       </c>
-      <c r="K19" s="6" t="n">
+      <c r="M19" s="7" t="n">
         <v>233654000</v>
       </c>
-      <c r="L19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="7" t="inlineStr"/>
+      <c r="N19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="6" t="inlineStr"/>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Khắc phục theo BBKT 1002/2026/VH-VT4 | Vật tư mua mới, chưa đề xuất trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1297,39 +1706,54 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Thanh cái đồng mạ bạc Busbar 400V - Thanh cái đồng mạ bạc
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Thanh cái đồng mạ bạc Busbar 400V</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Thanh cái đồng mạ bạc
 Kích thước: Dài x rộng x dày (850x125x10mm)
 Chiều dài: 850mm</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Thanh</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n">
+      <c r="G20" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="H20" s="7" t="n">
         <v>48000000</v>
       </c>
-      <c r="G20" s="6" t="n">
+      <c r="I20" s="7" t="n">
         <v>48000000</v>
       </c>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="6" t="n">
+      <c r="J20" s="6" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr"/>
+      <c r="L20" s="7" t="n">
         <v>48000000</v>
       </c>
-      <c r="K20" s="6" t="n">
+      <c r="M20" s="7" t="n">
         <v>48000000</v>
       </c>
-      <c r="L20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="7" t="inlineStr"/>
+      <c r="N20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="6" t="inlineStr"/>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay thế cho vật tư hư hỏng theo BBKT 37/2026/VH-VT4 | Vật tư mua mới, không đề xuất trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1340,39 +1764,54 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Thanh cái đồng V phân phối mạ bạc - Thanh cái đồng V phân phối mạ bạc
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Thanh cái đồng V phân phối mạ bạc</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Thanh cái đồng V phân phối mạ bạc
 Kích thước: 28x40x6mm
 Chiều dài: 920mm</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Thanh</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <v>48000000</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <v>192000000</v>
       </c>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="6" t="inlineStr"/>
+      <c r="K21" s="6" t="inlineStr"/>
+      <c r="L21" s="7" t="n">
         <v>48000000</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="M21" s="7" t="n">
         <v>192000000</v>
       </c>
-      <c r="L21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="6" t="inlineStr"/>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay thế cho vật tư hư hỏng theo BBKT 37/2026/VH-VT4 | Vật tư mua mới, không đề xuất trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1383,40 +1822,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Van điện từ 221S25F-S2TBC2 - Van điện từ 221S25F-S2TBC2,
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Van điện từ 221S25F-S2TBC2</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Van điện từ 221S25F-S2TBC2,
 Van 2 chiều, kích thước đường ống 1 inch,
 Điện áp cuộn điện từ (coil) 24 VDC,
 Nhà sản xuất: Parker</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Parker/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <v>22000000</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <v>22000000</v>
       </c>
-      <c r="H22" s="7" t="inlineStr"/>
-      <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="6" t="inlineStr"/>
+      <c r="K22" s="6" t="inlineStr"/>
+      <c r="L22" s="7" t="n">
         <v>22000000</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="M22" s="7" t="n">
         <v>22000000</v>
       </c>
-      <c r="L22" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="7" t="inlineStr"/>
+      <c r="N22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="6" t="inlineStr"/>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã ERP | Hệ thống xử lý nước thải (van điền nước bồn A polymer)76/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -1427,37 +1881,52 @@
           <t>2.46.35.037.CHN.00.000</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m - Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n">
+      <c r="G23" s="7" t="n">
         <v>35</v>
       </c>
-      <c r="F23" s="6" t="n">
+      <c r="H23" s="7" t="n">
+        <v>19300000</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>675500000</v>
+      </c>
+      <c r="J23" s="6" t="inlineStr"/>
+      <c r="K23" s="6" t="inlineStr"/>
+      <c r="L23" s="7" t="n">
         <v>18522000</v>
       </c>
-      <c r="G23" s="6" t="n">
+      <c r="M23" s="7" t="n">
         <v>648270000</v>
       </c>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="6" t="n">
-        <v>18522000</v>
-      </c>
-      <c r="K23" s="6" t="n">
-        <v>648270000</v>
-      </c>
-      <c r="L23" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="7" t="inlineStr"/>
+      <c r="N23" s="7" t="n">
+        <v>27230000</v>
+      </c>
+      <c r="O23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>2.46.35.037.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -1468,37 +1937,52 @@
           <t>2.46.35.019.CHN.00.000</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m - Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Ống khí nén/ tube, Model: SS-T8-S-065-20, OD: 1/2 inch, Length: 6m</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n">
+      <c r="G24" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F24" s="6" t="n">
+      <c r="H24" s="7" t="n">
         <v>19000000</v>
       </c>
-      <c r="G24" s="6" t="n">
+      <c r="I24" s="7" t="n">
         <v>38000000</v>
       </c>
-      <c r="H24" s="7" t="inlineStr"/>
-      <c r="I24" s="7" t="inlineStr"/>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="6" t="inlineStr"/>
+      <c r="K24" s="6" t="inlineStr"/>
+      <c r="L24" s="7" t="n">
         <v>19000000</v>
       </c>
-      <c r="K24" s="6" t="n">
+      <c r="M24" s="7" t="n">
         <v>38000000</v>
       </c>
-      <c r="L24" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="7" t="inlineStr"/>
+      <c r="N24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="6" t="inlineStr"/>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>2.46.35.019.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -1509,37 +1993,52 @@
           <t>4.82.22.013.USA.00.000</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6 - Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Stainless Steel Swagelok Tube Fitting, Union, 1/ 2 in. Tube OD; Order code: SS-810-6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="6" t="n">
+      <c r="H25" s="7" t="n">
         <v>1700000</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <v>3400000</v>
       </c>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr"/>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="6" t="inlineStr"/>
+      <c r="K25" s="6" t="inlineStr"/>
+      <c r="L25" s="7" t="n">
         <v>1700000</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="M25" s="7" t="n">
         <v>3400000</v>
       </c>
-      <c r="L25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="6" t="inlineStr"/>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>4.82.22.013.USA.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -1550,37 +2049,52 @@
           <t>4.82.22.025.CHN.00.000</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Đầu nối - Union Swagelok Model: SS-600-6 - Đầu nối - Union Swagelok Model: SS-600-6</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Đầu nối - Union Swagelok Model: SS-600-6</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n">
+      <c r="G26" s="7" t="n">
         <v>100</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="H26" s="7" t="n">
         <v>2600000</v>
       </c>
-      <c r="G26" s="6" t="n">
+      <c r="I26" s="7" t="n">
         <v>260000000</v>
       </c>
-      <c r="H26" s="7" t="inlineStr"/>
-      <c r="I26" s="7" t="inlineStr"/>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="6" t="inlineStr"/>
+      <c r="K26" s="6" t="inlineStr"/>
+      <c r="L26" s="7" t="n">
         <v>2600000</v>
       </c>
-      <c r="K26" s="6" t="n">
+      <c r="M26" s="7" t="n">
         <v>260000000</v>
       </c>
-      <c r="L26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="6" t="inlineStr"/>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>4.82.22.025.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -1591,37 +2105,52 @@
           <t>4.82.82.014.GER.00.000</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size - Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Cùm cố định ống/ Tube Support Strip, model: MS-TSS-6, 10 Channels, 3/8 inch, 10 mm Tube Size</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Swagelok/ Đức</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n">
+      <c r="G27" s="7" t="n">
         <v>15</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="H27" s="7" t="n">
         <v>200000</v>
       </c>
-      <c r="G27" s="6" t="n">
+      <c r="I27" s="7" t="n">
         <v>3000000</v>
       </c>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="6" t="n">
+      <c r="J27" s="6" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="7" t="n">
         <v>200000</v>
       </c>
-      <c r="K27" s="6" t="n">
+      <c r="M27" s="7" t="n">
         <v>3000000</v>
       </c>
-      <c r="L27" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="7" t="inlineStr"/>
+      <c r="N27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="6" t="inlineStr"/>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>4.82.82.014.GER.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -1632,9 +2161,14 @@
           <t>5.33.70.184.GER.99.000</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001 - Bộ điều khiển định vị Positioner:
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner, Model: TZIDC-V18345- 2020521001</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Bộ điều khiển định vị Positioner:
 - Model: TZIDC-V18345- 2020521001
 -Type: Double acting 
 -Sofw.Rev: 3 
@@ -1645,32 +2179,42 @@
 -NSX: ABB</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>ABB/ Đức</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F28" s="6" t="n">
+      <c r="G28" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H28" s="7" t="n">
         <v>85000000</v>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>170000000</v>
-      </c>
-      <c r="H28" s="7" t="inlineStr"/>
-      <c r="I28" s="7" t="inlineStr"/>
-      <c r="J28" s="6" t="n">
+      <c r="I28" s="7" t="n">
+        <v>425000000</v>
+      </c>
+      <c r="J28" s="6" t="inlineStr"/>
+      <c r="K28" s="6" t="inlineStr"/>
+      <c r="L28" s="7" t="n">
         <v>85000000</v>
       </c>
-      <c r="K28" s="6" t="n">
-        <v>170000000</v>
-      </c>
-      <c r="L28" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="n">
+        <v>425000000</v>
+      </c>
+      <c r="N28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="6" t="inlineStr"/>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>5.33.70.184.GER.99.000 | Thay thế các bộ positioner điều khiển damper gió SA bị xì khí nén của tổ máy S2 | Vật tư được đề xuất trong KHSXKD năm 2026,nhưng phát sinh hư hỏng thêm 2 bộ vượt nhu cầu dự kiến, nên đề xuất mua sắm bổ sung. Tên vật tư được đặt lại theo quy tắc chuẩn hóa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -1681,9 +2225,14 @@
           <t>3.96.13.144.USA.00.000</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire - Cảm biến nhiệt độ - Model: S14405PD3S350B0
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ Model: S14405PD3S350B0, Type: RTD PT100 3 Wire</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến nhiệt độ - Model: S14405PD3S350B0
 - NSX: MINCO 
 - Element: Platinum 
 - Element length: 6.4 mm 
@@ -1695,32 +2244,42 @@
 - Range: 0 - 260 °C</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Minco/ Mỹ</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n">
+      <c r="G29" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="6" t="n">
+      <c r="H29" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="G29" s="6" t="n">
+      <c r="I29" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="6" t="inlineStr"/>
+      <c r="K29" s="6" t="inlineStr"/>
+      <c r="L29" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="K29" s="6" t="n">
+      <c r="M29" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="L29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="7" t="inlineStr"/>
+      <c r="N29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="6" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>3.96.13.144.USA.00.000 | BBKT- 1008/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến nhiệt độ số 2 gối chặn BFPT B S2 báo lỗi.Vật tư có trong KH SXKD 2026 (mã KH TXBS.26.562). | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -1731,38 +2290,53 @@
           <t>3.96.13.320.USA.00.000</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb. - Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến đo khối lượng Load cell Part no: N39188-187; Capacity: 100Lb.
 NSX: MERRICK</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Merrick/ Mỹ</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n">
+      <c r="G30" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F30" s="6" t="n">
+      <c r="H30" s="7" t="n">
+        <v>56105000</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>112210000</v>
+      </c>
+      <c r="J30" s="6" t="inlineStr"/>
+      <c r="K30" s="6" t="inlineStr"/>
+      <c r="L30" s="7" t="n">
         <v>23000000</v>
       </c>
-      <c r="G30" s="6" t="n">
+      <c r="M30" s="7" t="n">
         <v>46000000</v>
       </c>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr"/>
-      <c r="J30" s="6" t="n">
-        <v>23000000</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>46000000</v>
-      </c>
-      <c r="L30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="n">
+        <v>66210000</v>
+      </c>
+      <c r="O30" s="6" t="inlineStr"/>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>3.96.13.320.USA.00.000 | BBKT- 1033/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến khối lượng than – máy cấp A tổ máy S3 báo sai giá trị.Vật tư không có trong KH SXKD 2026. | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -1773,41 +2347,56 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm) - LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Bộ đo mức LEVEL TRANSMITTER; Loại: Ultrasonic LT (sóng siêu âm)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>LEVEL TRANSMITTER Loại: Ultrasonic LT (sóng siêu âm) 
 Model: LST400 Y0/S15/N1/P6/A1/H1/SC6/B2/CR/M5
 Range: 0.5m to 15m Signal: 4 - 20 mA 
 Supply power: 115 to 230 V AC or 24 V DC.
 NSX: ABB</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>ABB/ Đức</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n">
+      <c r="G31" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="H31" s="7" t="n">
         <v>189000000</v>
       </c>
-      <c r="G31" s="6" t="n">
+      <c r="I31" s="7" t="n">
         <v>189000000</v>
       </c>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="6" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr"/>
+      <c r="L31" s="7" t="n">
         <v>189000000</v>
       </c>
-      <c r="K31" s="6" t="n">
+      <c r="M31" s="7" t="n">
         <v>189000000</v>
       </c>
-      <c r="L31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="6" t="inlineStr"/>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã VT | BBKT- 955/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến báo mức nước tổng kênh tuần hoàn tổ máy S1 báo sai giá trị. | Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1818,9 +2407,14 @@
           <t>3.96.11.033.SIN.00.000</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG1A02A1AS5M5D4T1Q4 - Cảm biến áp suất (Pressure transmitter) 
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG1A02A1AS5M5D4T1Q4</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến áp suất (Pressure transmitter) 
 Model: 2051CG1A02A1AS5M5D4T1Q4 
 Output Hart: 4-20mA 
 Supply: 10.5 – 42.4 VDC 
@@ -1828,32 +2422,42 @@
 NSX: Rosemount</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Rosemount/ Singapore</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n">
+      <c r="G32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="6" t="n">
+      <c r="H32" s="7" t="n">
         <v>145000000</v>
       </c>
-      <c r="G32" s="6" t="n">
+      <c r="I32" s="7" t="n">
         <v>145000000</v>
       </c>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr"/>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="6" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr"/>
+      <c r="L32" s="7" t="n">
         <v>145000000</v>
       </c>
-      <c r="K32" s="6" t="n">
+      <c r="M32" s="7" t="n">
         <v>145000000</v>
       </c>
-      <c r="L32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="7" t="inlineStr"/>
+      <c r="N32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="6" t="inlineStr"/>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>3.96.11.033.SIN.00.000 | BBKT- 1027/2026/VH-VT4_ Kiểm tra, khắc phục bộ chuyển đổi tín hiệu đo áp suất gió SA tầng F tổ máy S1 báo sai giá trị. | Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -1864,9 +2468,14 @@
           <t>5.33.70.823.SIN.98.000</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Bộ đo áp suất - Differential pressure transmitter with Intergral Manifold, Transmitter model: 2051CD1A02A1AS5 M5D4T1Q4 - Bộ đo áp suất - Differential pressure transmitter with Intergral Manifold, Transmitter model: 2051CD1A02A1AS5 M5D4T1Q4
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Bộ đo áp suất - Differential pressure transmitter with Intergral Manifold, Transmitter model: 2051CD1A02A1AS5 M5D4T1Q4</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Bộ đo áp suất - Differential pressure transmitter with Intergral Manifold, Transmitter model: 2051CD1A02A1AS5 M5D4T1Q4
 Output Hart: 4-20mA 
 Supply: 10.5 – 42.4 VDC 
 CAL: 0 to 600 mmH20) 
@@ -1874,32 +2483,42 @@
 NSX: Rosemount</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Rosemount/ Singapore</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E33" s="6" t="n">
+      <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="6" t="n">
+      <c r="H33" s="7" t="n">
         <v>247000000</v>
       </c>
-      <c r="G33" s="6" t="n">
+      <c r="I33" s="7" t="n">
         <v>247000000</v>
       </c>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="6" t="inlineStr"/>
+      <c r="K33" s="6" t="inlineStr"/>
+      <c r="L33" s="7" t="n">
         <v>247000000</v>
       </c>
-      <c r="K33" s="6" t="n">
+      <c r="M33" s="7" t="n">
         <v>247000000</v>
       </c>
-      <c r="L33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="7" t="inlineStr"/>
+      <c r="N33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="6" t="inlineStr"/>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>5.33.70.823.SIN.98.000 | BBKT- 1013/2026/VH-VT4_ Kiểm tra, khắc phục điểm đo chênh áp đầu hút quạt gió cấp 2B tổ máy S3 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -1910,40 +2529,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN50 - Công tơ nước dạng cơ, kích thước DN50, 4 lỗ bulong Ø16 ở mỗi đầu bích;
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN50</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN50, 4 lỗ bulong Ø16 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Zenner/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E34" s="6" t="n">
+      <c r="G34" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="H34" s="7" t="n">
         <v>5001000</v>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="I34" s="7" t="n">
         <v>5001000</v>
       </c>
-      <c r="H34" s="7" t="inlineStr"/>
-      <c r="I34" s="7" t="inlineStr"/>
-      <c r="J34" s="6" t="n">
+      <c r="J34" s="6" t="inlineStr"/>
+      <c r="K34" s="6" t="inlineStr"/>
+      <c r="L34" s="7" t="n">
         <v>5001000</v>
       </c>
-      <c r="K34" s="6" t="n">
+      <c r="M34" s="7" t="n">
         <v>5001000</v>
       </c>
-      <c r="L34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="7" t="inlineStr"/>
+      <c r="N34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="6" t="inlineStr"/>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp vận hành hệ thống Hydro | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -1954,40 +2588,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu - Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu;
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN15, ren ngoài 2 đầu;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Zenner/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E35" s="6" t="n">
+      <c r="G35" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="6" t="n">
+      <c r="H35" s="7" t="n">
         <v>375000</v>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="I35" s="7" t="n">
         <v>375000</v>
       </c>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr"/>
-      <c r="J35" s="6" t="n">
+      <c r="J35" s="6" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr"/>
+      <c r="L35" s="7" t="n">
         <v>375000</v>
       </c>
-      <c r="K35" s="6" t="n">
+      <c r="M35" s="7" t="n">
         <v>375000</v>
       </c>
-      <c r="L35" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="7" t="inlineStr"/>
+      <c r="N35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="6" t="inlineStr"/>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp cho phòng thí nghiệm | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -1998,37 +2647,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304 - Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Đầu chuyển hàn – ren ngoài DN15, vật liệu inox 304</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n">
+      <c r="G36" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F36" s="6" t="n">
+      <c r="H36" s="7" t="n">
         <v>28000</v>
       </c>
-      <c r="G36" s="6" t="n">
+      <c r="I36" s="7" t="n">
         <v>56000</v>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr"/>
-      <c r="J36" s="6" t="n">
+      <c r="J36" s="6" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr"/>
+      <c r="L36" s="7" t="n">
         <v>28000</v>
       </c>
-      <c r="K36" s="6" t="n">
+      <c r="M36" s="7" t="n">
         <v>56000</v>
       </c>
-      <c r="L36" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="7" t="inlineStr"/>
+      <c r="N36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="6" t="inlineStr"/>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp cho phòng thí nghiệm | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -2039,37 +2703,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Rắc co ren trong DN15, vật liệu inox 304 - Rắc co ren trong DN15, vật liệu inox 304</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Rắc co ren trong DN15, vật liệu inox 304</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Rắc co ren trong DN15, vật liệu inox 304</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E37" s="6" t="n">
+      <c r="G37" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F37" s="6" t="n">
+      <c r="H37" s="7" t="n">
         <v>104000</v>
       </c>
-      <c r="G37" s="6" t="n">
+      <c r="I37" s="7" t="n">
         <v>208000</v>
       </c>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="6" t="n">
+      <c r="J37" s="6" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr"/>
+      <c r="L37" s="7" t="n">
         <v>104000</v>
       </c>
-      <c r="K37" s="6" t="n">
+      <c r="M37" s="7" t="n">
         <v>208000</v>
       </c>
-      <c r="L37" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="7" t="inlineStr"/>
+      <c r="N37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6" t="inlineStr"/>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp cho phòng thí nghiệm | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -2080,40 +2759,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN125 - Công tơ nước dạng cơ, kích thước DN125, 8 lỗ bulong Ø16 ở mỗi đầu bích;
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN125</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN125, 8 lỗ bulong Ø16 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Zenner/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="G38" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="H38" s="7" t="n">
         <v>9660000</v>
       </c>
-      <c r="G38" s="6" t="n">
+      <c r="I38" s="7" t="n">
         <v>19320000</v>
       </c>
-      <c r="H38" s="7" t="inlineStr"/>
-      <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="6" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr"/>
+      <c r="L38" s="7" t="n">
         <v>9660000</v>
       </c>
-      <c r="K38" s="6" t="n">
+      <c r="M38" s="7" t="n">
         <v>19320000</v>
       </c>
-      <c r="L38" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="7" t="inlineStr"/>
+      <c r="N38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="6" t="inlineStr"/>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp vận hành hệ thống hoàn nguyên CPP 4-4MR | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -2124,40 +2818,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN150 - Công tơ nước dạng cơ, kích thước DN150, 8 lỗ bulong Ø20 ở mỗi đầu bích;
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN150</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN150, 8 lỗ bulong Ø20 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Zenner/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="H39" s="7" t="n">
         <v>13800000</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="I39" s="7" t="n">
         <v>82800000</v>
       </c>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
-      <c r="J39" s="6" t="n">
+      <c r="J39" s="6" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr"/>
+      <c r="L39" s="7" t="n">
         <v>13800000</v>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="M39" s="7" t="n">
         <v>82800000</v>
       </c>
-      <c r="L39" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="7" t="inlineStr"/>
+      <c r="N39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="6" t="inlineStr"/>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp vận hành cho lò hơi, tuabin 3 tổ máy | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -2168,40 +2877,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN200 PN16 - Công tơ nước dạng cơ, kích thước DN200 PN16, 12 lỗ bulong Ø20 ở mỗi đầu bích;
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN200 PN16</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN200 PN16, 12 lỗ bulong Ø20 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước khử khoáng);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Zenner/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="G40" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F40" s="6" t="n">
+      <c r="H40" s="7" t="n">
         <v>14000000</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="I40" s="7" t="n">
         <v>28000000</v>
       </c>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr"/>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="6" t="inlineStr"/>
+      <c r="K40" s="6" t="inlineStr"/>
+      <c r="L40" s="7" t="n">
         <v>14000000</v>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="M40" s="7" t="n">
         <v>28000000</v>
       </c>
-      <c r="L40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="6" t="inlineStr"/>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Demi cấp vận hành hệ thống xử lý nước VT4-4MR | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -2212,40 +2936,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Công tơ nước dạng cơ, kích thước DN100 - Công tơ nước dạng cơ, kích thước DN100, 8 lỗ bulong Ø16 ở mỗi đầu bích;
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN100</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Công tơ nước dạng cơ, kích thước DN100, 8 lỗ bulong Ø16 ở mỗi đầu bích;
 Vật liệu: Cast iron;
 Môi chất làm việc: nước sạch (nước dịch vụ);
 Công tơ có giấy chứng nhận hiệu chuẩn.</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Zenner/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="G41" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="H41" s="7" t="n">
         <v>6726000</v>
       </c>
-      <c r="G41" s="6" t="n">
+      <c r="I41" s="7" t="n">
         <v>6726000</v>
       </c>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="6" t="n">
+      <c r="J41" s="6" t="inlineStr"/>
+      <c r="K41" s="6" t="inlineStr"/>
+      <c r="L41" s="7" t="n">
         <v>6726000</v>
       </c>
-      <c r="K41" s="6" t="n">
+      <c r="M41" s="7" t="n">
         <v>6726000</v>
       </c>
-      <c r="L41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="6" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Lắp đặt cho đường nước Service cấp bù áp nước chữa cháy | Báo cáo số 2558/KTATChưa đề xuất trong KHSXKD.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -2256,40 +2995,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Cảm biến đo lưu lượng siêu âm
-(Ultrasonic Flowmeter Transducer) - Cảm biến đo lưu lượng siêu âm (Ultrasonic Flowmeter Transducer)
+(Ultrasonic Flowmeter Transducer)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến đo lưu lượng siêu âm (Ultrasonic Flowmeter Transducer)
 Model: LTE1-B
 NSX: Jain Technology</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Jain/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E42" s="6" t="n">
+      <c r="G42" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F42" s="6" t="n">
+      <c r="H42" s="7" t="n">
         <v>162000000</v>
       </c>
-      <c r="G42" s="6" t="n">
+      <c r="I42" s="7" t="n">
         <v>324000000</v>
       </c>
-      <c r="H42" s="7" t="inlineStr"/>
-      <c r="I42" s="7" t="inlineStr"/>
-      <c r="J42" s="6" t="n">
+      <c r="J42" s="6" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr"/>
+      <c r="L42" s="7" t="n">
         <v>162000000</v>
       </c>
-      <c r="K42" s="6" t="n">
+      <c r="M42" s="7" t="n">
         <v>324000000</v>
       </c>
-      <c r="L42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="6" t="inlineStr"/>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã VT | BBKT- 1041/2026/VH-VT4_ Kiểm tra, khắc phục thiết bị giám sát lưu lượng bơm nước biển  S2 báo lỗi.Vật tư không có trong KH SXKD 2026. | Vật tư đề xuất nâng cấp tương đương.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -2300,40 +3054,55 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound) - Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound)
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound)</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Hợp chất Silicone tiếp âm và bôi trơn(Silicone Compound)
 Applicatinon: Sealant and Lubricant
 Cautinon: Mix thoroughly before use
 NSX: Jain Technology</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Jain/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Hộp</t>
         </is>
       </c>
-      <c r="E43" s="6" t="n">
+      <c r="G43" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F43" s="6" t="n">
+      <c r="H43" s="7" t="n">
         <v>1300000</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="I43" s="7" t="n">
         <v>5200000</v>
       </c>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="6" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr"/>
+      <c r="L43" s="7" t="n">
         <v>1300000</v>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="M43" s="7" t="n">
         <v>5200000</v>
       </c>
-      <c r="L43" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="7" t="inlineStr"/>
+      <c r="N43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="6" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã VT | BBKT- 1041/2026/VH-VT4_ Kiểm tra, khắc phục thiết bị giám sát lưu lượng bơm nước biển  S2 báo lỗi.Vật tư không có trong KH SXKD 2026. |</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -2344,40 +3113,55 @@
           <t>5.33.85.167.JPN.00.000</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2 - Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Đầu dò Oxy thừa Zirconia/ Zirconia Detector, Model: NS-3000, Style: S2
 - Suffix: -4-1-X3-2-2-2-1-1
 - AMB.Temp: -20 ~ 150 ºC
 NSX: Horiba</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Horiba/ Nhật Bản</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n">
+      <c r="G44" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F44" s="6" t="n">
+      <c r="H44" s="7" t="n">
         <v>669500000</v>
       </c>
-      <c r="G44" s="6" t="n">
+      <c r="I44" s="7" t="n">
         <v>669500000</v>
       </c>
-      <c r="H44" s="7" t="inlineStr"/>
-      <c r="I44" s="7" t="inlineStr"/>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="6" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr"/>
+      <c r="L44" s="7" t="n">
         <v>669500000</v>
       </c>
-      <c r="K44" s="6" t="n">
+      <c r="M44" s="7" t="n">
         <v>669500000</v>
       </c>
-      <c r="L44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="7" t="inlineStr"/>
+      <c r="N44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="6" t="inlineStr"/>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>5.33.85.167.JPN.00.000 | BBKT- 1159/2026/VH-VT4_ Kiểm tra, khắc phục thiết bị đo nồng độ oxy thừa trong khói thoát lò hơi nhánh 1A tổ máy S1 báo lỗi.Vật tư có trong KH SXKD 2026 (mã KH:TX.26.2202, 01 bộ). | Mua sắm dự phòng hết tồn kho thiết bị giám sát quan trọng.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -2388,9 +3172,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD) - Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Thiết bị chống sét lan truyền / Chống nhiễu cấp nguồn (Surge Protective Device - SPD)
 Model: MA3145-230-2-R
 - Điện áp hoạt động tối đa (Max working voltage): ≥ 270 VAC.
 - Điện áp định mức (Voltage rating): 230 VAC.
@@ -2398,32 +3187,42 @@
 NSX: Cooper Crouse-Hinds MTL / Eaton</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Eaton/ Slovenia</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E45" s="6" t="n">
+      <c r="G45" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F45" s="6" t="n">
+      <c r="H45" s="7" t="n">
         <v>35000000</v>
       </c>
-      <c r="G45" s="6" t="n">
+      <c r="I45" s="7" t="n">
         <v>105000000</v>
       </c>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="6" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr"/>
+      <c r="L45" s="7" t="n">
         <v>35000000</v>
       </c>
-      <c r="K45" s="6" t="n">
+      <c r="M45" s="7" t="n">
         <v>105000000</v>
       </c>
-      <c r="L45" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="7" t="inlineStr"/>
+      <c r="N45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="6" t="inlineStr"/>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã VT | BBKT- 1089/2026/VH-VT4_ Kiểm tra, khắc phục các con đo lưu lượng nước biển S3 không. hiển thị. | Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -2434,39 +3233,54 @@
           <t>3.96.13.071.KOR.00.000</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa - Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa, Model cảm biến: NBFS-FC2000, Length: 2825 mm, Sensor MTG Size: PT1"M, Material: Stainless Steel
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa, Model cảm biến: NBFS-FC2000, Length: 2825 mm, Sensor MTG Size: PT1"M, Material: Stainless Steel
 Dây tín hiệu quang cho cảm biến phát hiện ngọn lửa (Model cảm biến phát hiện ngọn lửa: NBFS-FC2000). - Overall dimension: 20Ø*2825mm with 80Ø*8t Flange - Length: 2825 mm - Sensor MTG Size: PT1"M - Material: Stainless Steel - Fiber Optic Conductor: + Material: Glass Optical Multi Component + Clad Diameter: 0.025mm ent + Bundle Diameter: 3mm + Operating Temperature: Max. 400°C(750°F) - OD tube: Flexible tube 3/8’’ - Detail “C” - Lens: + Material : Quartz + Operating Temperature: Max. 1680°C 
 NSX: Nambukeng</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Nambukeng/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
         <is>
           <t>Sợi</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n">
+      <c r="G46" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="6" t="n">
+      <c r="H46" s="7" t="n">
         <v>135000000</v>
       </c>
-      <c r="G46" s="6" t="n">
+      <c r="I46" s="7" t="n">
         <v>270000000</v>
       </c>
-      <c r="H46" s="7" t="inlineStr"/>
-      <c r="I46" s="7" t="inlineStr"/>
-      <c r="J46" s="6" t="n">
+      <c r="J46" s="6" t="inlineStr"/>
+      <c r="K46" s="6" t="inlineStr"/>
+      <c r="L46" s="7" t="n">
         <v>135000000</v>
       </c>
-      <c r="K46" s="6" t="n">
+      <c r="M46" s="7" t="n">
         <v>270000000</v>
       </c>
-      <c r="L46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="6" t="inlineStr"/>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>3.96.13.071.KOR.00.000 | BBKT- 1103/2026/VH-VT4_ Kiểm tra, khắc phục bộ giám sát ngọn lửa vòi than E1, E3 – S2 bị lỗi.  | Vật tư có trong KH SXKD 2026 (mã TX.26.2210, 01 sợi).</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -2477,41 +3291,56 @@
           <t>3.34.40.009.IND.00.000</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Công tắc lưu lượng (Flow Switch) - Công tắc lưu lượng (Flow Switch)
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch)</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Công tắc lưu lượng (Flow Switch)
 Model: WP/FS-25VFL
 Switch : SPDT Snap Acting Micro
 Rating : 5A 250VAC 
 NSX: Dag Process Instruments Pvt. Ltd</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Dag Process Instruments Pvt. Ltd/ Ấn Độ</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E47" s="6" t="n">
+      <c r="G47" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="6" t="n">
+      <c r="H47" s="7" t="n">
         <v>38000000</v>
       </c>
-      <c r="G47" s="6" t="n">
+      <c r="I47" s="7" t="n">
         <v>38000000</v>
       </c>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="6" t="n">
+      <c r="J47" s="6" t="inlineStr"/>
+      <c r="K47" s="6" t="inlineStr"/>
+      <c r="L47" s="7" t="n">
         <v>38000000</v>
       </c>
-      <c r="K47" s="6" t="n">
+      <c r="M47" s="7" t="n">
         <v>38000000</v>
       </c>
-      <c r="L47" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="7" t="inlineStr"/>
+      <c r="N47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="6" t="inlineStr"/>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã VT | BBKT- 1122/2026/VH-VT4_ Kiểm tra, lỗi tín hiệu lưu lượng gió chèn 1B – ESP -  S1 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -2522,9 +3351,14 @@
           <t>0</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Thiết bị đo lưu lượng (Flow Transmitter): - Model: 2051CD2A02A1AS5M5D4T1C1Q4 - Thiết bị đo lưu lượng (Flow Transmitter): - Model: 2051CD2A02A1AS5M5D4T1C1Q4
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Thiết bị đo lưu lượng (Flow Transmitter): - Model: 2051CD2A02A1AS5M5D4T1C1Q4</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Thiết bị đo lưu lượng (Flow Transmitter): - Model: 2051CD2A02A1AS5M5D4T1C1Q4
 Output Hart: 4-20mA 
 Supply: 10.5 – 42.4 VDC 
 CAL: 0 to 1470,24 mmH20) 
@@ -2532,32 +3366,42 @@
 NSX: Rosemount</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Rosemount/ Singapore</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E48" s="6" t="n">
+      <c r="G48" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F48" s="6" t="n">
+      <c r="H48" s="7" t="n">
         <v>230000000</v>
       </c>
-      <c r="G48" s="6" t="n">
+      <c r="I48" s="7" t="n">
         <v>230000000</v>
       </c>
-      <c r="H48" s="7" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr"/>
-      <c r="J48" s="6" t="n">
+      <c r="J48" s="6" t="inlineStr"/>
+      <c r="K48" s="6" t="inlineStr"/>
+      <c r="L48" s="7" t="n">
         <v>230000000</v>
       </c>
-      <c r="K48" s="6" t="n">
+      <c r="M48" s="7" t="n">
         <v>230000000</v>
       </c>
-      <c r="L48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="7" t="inlineStr"/>
+      <c r="N48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="6" t="inlineStr"/>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>5.33.70.894.SIN.00.000 | BBKT- 1104/2026/VH-VT4_ Kiểm tra, khắc phục điểm đo lưu lượng gió cấp 2A tổ máy S2 báo lỗi.  | Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -2568,9 +3412,14 @@
           <t>3.96.13.165.KOR.00.000</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor - Cảm biến tiệm cận/proximity sensor
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
 - Model: PR30-10AC
 Đường kính cạnh phát hiện: 30mm
 - Điện áp hoạt động: 100-240 Vac
@@ -2578,32 +3427,42 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Autonics/ China</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E49" s="6" t="n">
+      <c r="G49" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="6" t="n">
+      <c r="H49" s="7" t="n">
         <v>1219000</v>
       </c>
-      <c r="G49" s="6" t="n">
+      <c r="I49" s="7" t="n">
         <v>2438000</v>
       </c>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="6" t="n">
+      <c r="J49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr"/>
+      <c r="L49" s="7" t="n">
         <v>1219000</v>
       </c>
-      <c r="K49" s="6" t="n">
+      <c r="M49" s="7" t="n">
         <v>2438000</v>
       </c>
-      <c r="L49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="7" t="inlineStr"/>
+      <c r="N49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="6" t="inlineStr"/>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>3.96.13.165.KOR.00.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương, kích thước theo file BBKT đính kèm</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -2614,9 +3473,14 @@
           <t>3.96.13.114.KOR.99.000</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Cảm biến tiệm cận/proximity sensor - Cảm biến tiệm cận/proximity sensor
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến tiệm cận/proximity sensor
 - Model: PR18-8AO
 - Đường kính đầu dò: 18mm
 - Điện áp hoạt động: 100-240 Vac
@@ -2624,32 +3488,42 @@
 - Protection: IP67</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Autonics/ China</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n">
+      <c r="G50" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="H50" s="7" t="n">
         <v>1150000</v>
       </c>
-      <c r="G50" s="6" t="n">
+      <c r="I50" s="7" t="n">
         <v>1150000</v>
       </c>
-      <c r="H50" s="7" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
-      <c r="J50" s="6" t="n">
+      <c r="J50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr"/>
+      <c r="L50" s="7" t="n">
         <v>1150000</v>
       </c>
-      <c r="K50" s="6" t="n">
+      <c r="M50" s="7" t="n">
         <v>1150000</v>
       </c>
-      <c r="L50" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="7" t="inlineStr"/>
+      <c r="N50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="6" t="inlineStr"/>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>3.96.13.114.KOR.99.000 | Sửa chữa Tời điện số 15 tấn A Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -2660,40 +3534,55 @@
           <t>2.05.80.082.KOR.00.000</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Hanger clamps (out doors) (kẹp giữ đường ray cáp điện) - Hanger clamps (out doors) (kẹp giữ đường ray cáp điện): Model: EH-2-001
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Hanger clamps (out doors) (kẹp giữ đường ray cáp điện)</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Hanger clamps (out doors) (kẹp giữ đường ray cáp điện): Model: EH-2-001
  - Material: Galvanized Steel 
 +Epoxy Insulator Dome
  - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="G51" s="7" t="n">
         <v>1284</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="H51" s="7" t="n">
+        <v>465000</v>
+      </c>
+      <c r="I51" s="7" t="n">
+        <v>597060000</v>
+      </c>
+      <c r="J51" s="6" t="inlineStr"/>
+      <c r="K51" s="6" t="inlineStr"/>
+      <c r="L51" s="7" t="n">
         <v>535000</v>
       </c>
-      <c r="G51" s="6" t="n">
+      <c r="M51" s="7" t="n">
         <v>686940000</v>
       </c>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="6" t="n">
-        <v>535000</v>
-      </c>
-      <c r="K51" s="6" t="n">
-        <v>686940000</v>
-      </c>
-      <c r="L51" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="7" t="inlineStr"/>
+      <c r="N51" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="6" t="inlineStr"/>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>2.05.80.082.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 675/2026/VH-VT4; 435/2026/VH-VT4; 475/2026/VH-VT4; 558/2026/VH-VT4; 468/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -2704,39 +3593,54 @@
           <t>3.34.20.134.CHN.00.000</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Pendant control station:
-Type: XAC-A12713 - Pendant control station:
 Type: XAC-A12713</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Pendant control station:
+Type: XAC-A12713</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="G52" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F52" s="6" t="n">
+      <c r="H52" s="7" t="n">
         <v>5784000</v>
       </c>
-      <c r="G52" s="6" t="n">
+      <c r="I52" s="7" t="n">
         <v>5784000</v>
       </c>
-      <c r="H52" s="7" t="inlineStr"/>
-      <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="6" t="n">
+      <c r="J52" s="6" t="inlineStr"/>
+      <c r="K52" s="6" t="inlineStr"/>
+      <c r="L52" s="7" t="n">
         <v>5784000</v>
       </c>
-      <c r="K52" s="6" t="n">
+      <c r="M52" s="7" t="n">
         <v>5784000</v>
       </c>
-      <c r="L52" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="7" t="inlineStr"/>
+      <c r="N52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="6" t="inlineStr"/>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>3.34.20.134.CHN.00.000 | Sửa chữa tời điện Tời điện số 15 tấn B Khu vực máy nghiền S3 theo BBKT 675/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -2747,41 +3651,56 @@
           <t>5.05.65.658.KOR.00.000</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Collector (chổi tiếp điện từ thanh ray) - Collector (chổi tiếp điện từ thanh ray):
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Collector (chổi tiếp điện từ thanh ray)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Collector (chổi tiếp điện từ thanh ray):
 - Iđm: 60A;
 - Uđm: 400VAC;
 - Material: Copper
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="G53" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="F53" s="6" t="n">
+      <c r="H53" s="7" t="n">
         <v>2265000</v>
       </c>
-      <c r="G53" s="6" t="n">
+      <c r="I53" s="7" t="n">
         <v>81540000</v>
       </c>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="6" t="n">
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="7" t="n">
         <v>2265000</v>
       </c>
-      <c r="K53" s="6" t="n">
+      <c r="M53" s="7" t="n">
         <v>81540000</v>
       </c>
-      <c r="L53" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="7" t="inlineStr"/>
+      <c r="N53" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="6" t="inlineStr"/>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>5.05.65.658.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4; 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -2792,39 +3711,54 @@
           <t>4.90.80.030.KOR.00.000</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover) - Joint cover (bao che giữa các khớp nối đường ray cáp điện):
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>Bao che giữa các khớp nối đường ray cáp điện (Joint cover)</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Joint cover (bao che giữa các khớp nối đường ray cáp điện):
 - Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E54" s="6" t="n">
+      <c r="G54" s="7" t="n">
         <v>235</v>
       </c>
-      <c r="F54" s="6" t="n">
+      <c r="H54" s="7" t="n">
         <v>66000</v>
       </c>
-      <c r="G54" s="6" t="n">
+      <c r="I54" s="7" t="n">
         <v>15510000</v>
       </c>
-      <c r="H54" s="7" t="inlineStr"/>
-      <c r="I54" s="7" t="inlineStr"/>
-      <c r="J54" s="6" t="n">
+      <c r="J54" s="6" t="inlineStr"/>
+      <c r="K54" s="6" t="inlineStr"/>
+      <c r="L54" s="7" t="n">
         <v>66000</v>
       </c>
-      <c r="K54" s="6" t="n">
+      <c r="M54" s="7" t="n">
         <v>15510000</v>
       </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="inlineStr"/>
+      <c r="N54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="inlineStr"/>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>4.90.80.030.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -2835,38 +3769,53 @@
           <t>4.90.80.027.KOR.00.000</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Nắp che phía cuối đường ray cáp điện (End cap) - Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Nắp che phía cuối đường ray cáp điện (End cap)- Material: PVC
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E55" s="6" t="n">
+      <c r="G55" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="F55" s="6" t="n">
+      <c r="H55" s="7" t="n">
         <v>68000</v>
       </c>
-      <c r="G55" s="6" t="n">
+      <c r="I55" s="7" t="n">
         <v>2176000</v>
       </c>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="6" t="n">
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
+      <c r="L55" s="7" t="n">
         <v>68000</v>
       </c>
-      <c r="K55" s="6" t="n">
+      <c r="M55" s="7" t="n">
         <v>2176000</v>
       </c>
-      <c r="L55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="7" t="inlineStr"/>
+      <c r="N55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="inlineStr"/>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>4.90.80.027.KOR.00.000 | Sửa chữa tời điện các vị trí S3 theo BBKT 435/2026/VH-VT4; 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -2877,9 +3826,14 @@
           <t>2.08.37.001.KOR.97.000</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Trolley-bar (thanh ray cấp nguồn) - Trolley-bar (thanh ray cấp nguồn):
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn)</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Trolley-bar (thanh ray cấp nguồn):
 - Iđm: 60A;
 - Uđm: 400VAC;
 - Length: 3m / cây
@@ -2887,32 +3841,42 @@
 - Maker: EunchangT&amp;C</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>Cây</t>
         </is>
       </c>
-      <c r="E56" s="6" t="n">
+      <c r="G56" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="F56" s="6" t="n">
+      <c r="H56" s="7" t="n">
         <v>909000</v>
       </c>
-      <c r="G56" s="6" t="n">
+      <c r="I56" s="7" t="n">
         <v>25452000</v>
       </c>
-      <c r="H56" s="7" t="inlineStr"/>
-      <c r="I56" s="7" t="inlineStr"/>
-      <c r="J56" s="6" t="n">
+      <c r="J56" s="6" t="inlineStr"/>
+      <c r="K56" s="6" t="inlineStr"/>
+      <c r="L56" s="7" t="n">
         <v>909000</v>
       </c>
-      <c r="K56" s="6" t="n">
+      <c r="M56" s="7" t="n">
         <v>25452000</v>
       </c>
-      <c r="L56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="7" t="inlineStr"/>
+      <c r="N56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="inlineStr"/>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>2.08.37.001.KOR.97.000 | Sửa chữa tời điện Tời điện 15 tấn quạt gió 2B theo BBKT 435/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -2923,41 +3887,56 @@
           <t>4.82.32.060.KOR.99.000</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Joint keeper (khớp nối các thanh ray) - Joint keeper (khớp nối các thanh ray):
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Joint keeper (khớp nối các thanh ray)</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Joint keeper (khớp nối các thanh ray):
 - Iđm: 60A;
 - Uđm: 400VAC;
 - Material: Copper
 - Maker: Eunchang T&amp;C</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Eunchang/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="G57" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="H57" s="7" t="n">
         <v>47000</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="I57" s="7" t="n">
         <v>1128000</v>
       </c>
-      <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="6" t="n">
+      <c r="J57" s="6" t="inlineStr"/>
+      <c r="K57" s="6" t="inlineStr"/>
+      <c r="L57" s="7" t="n">
         <v>47000</v>
       </c>
-      <c r="K57" s="6" t="n">
+      <c r="M57" s="7" t="n">
         <v>1128000</v>
       </c>
-      <c r="L57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="7" t="inlineStr"/>
+      <c r="N57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6" t="inlineStr"/>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>4.82.32.060.KOR.99.000 | Sửa chữa tời điện Tời điện 15 tấn quạt gió 2B theo BBKT 435/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -2968,37 +3947,52 @@
           <t>3.34.20.131.CHN.00.000</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Pendant control station, Type: XAC-A8713 - Pendant control station, Type: XAC-A8713</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Pendant control station, Type: XAC-A8713</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Pendant control station, Type: XAC-A8713</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E58" s="6" t="n">
+      <c r="G58" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F58" s="6" t="n">
+      <c r="H58" s="7" t="n">
         <v>6900000</v>
       </c>
-      <c r="G58" s="6" t="n">
+      <c r="I58" s="7" t="n">
         <v>6900000</v>
       </c>
-      <c r="H58" s="7" t="inlineStr"/>
-      <c r="I58" s="7" t="inlineStr"/>
-      <c r="J58" s="6" t="n">
+      <c r="J58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr"/>
+      <c r="L58" s="7" t="n">
         <v>6900000</v>
       </c>
-      <c r="K58" s="6" t="n">
+      <c r="M58" s="7" t="n">
         <v>6900000</v>
       </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="inlineStr"/>
+      <c r="N58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6" t="inlineStr"/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>3.34.20.131.CHN.00.000 | Sửa chữa Tời điện 30 tấn quạt khói theo BBKT 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -3009,10 +4003,15 @@
           <t>3.34.20.133.CHN.99.000</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>Pendant control station:
-Type: XAC-A6913 - Pendant control station:
+Type: XAC-A6913</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Pendant control station:
 Type: XAC-A6913
 Control station composition: 06 push buttons + 01 emergency stop
 Product compatibility: 
@@ -3020,32 +4019,42 @@
 Color: Yellow</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E59" s="6" t="n">
+      <c r="G59" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="6" t="n">
+      <c r="H59" s="7" t="n">
         <v>13319000</v>
       </c>
-      <c r="G59" s="6" t="n">
+      <c r="I59" s="7" t="n">
         <v>13319000</v>
       </c>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="6" t="n">
+      <c r="J59" s="6" t="inlineStr"/>
+      <c r="K59" s="6" t="inlineStr"/>
+      <c r="L59" s="7" t="n">
         <v>13319000</v>
       </c>
-      <c r="K59" s="6" t="n">
+      <c r="M59" s="7" t="n">
         <v>13319000</v>
       </c>
-      <c r="L59" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="7" t="inlineStr"/>
+      <c r="N59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="6" t="inlineStr"/>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 10 tấn quạt khói theo BBKT 475/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -3056,38 +4065,53 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 3 tấn - Lưỡi gà móc cẩu 3 tấn
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 3 tấn
 Kích thước: rộng 25mm x dài 60mm</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>MT/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E60" s="6" t="n">
+      <c r="G60" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F60" s="6" t="n">
+      <c r="H60" s="7" t="n">
         <v>610000</v>
       </c>
-      <c r="G60" s="6" t="n">
+      <c r="I60" s="7" t="n">
         <v>610000</v>
       </c>
-      <c r="H60" s="7" t="inlineStr"/>
-      <c r="I60" s="7" t="inlineStr"/>
-      <c r="J60" s="6" t="n">
+      <c r="J60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr"/>
+      <c r="L60" s="7" t="n">
         <v>610000</v>
       </c>
-      <c r="K60" s="6" t="n">
+      <c r="M60" s="7" t="n">
         <v>610000</v>
       </c>
-      <c r="L60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="7" t="inlineStr"/>
+      <c r="N60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="6" t="inlineStr"/>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -3098,38 +4122,53 @@
           <t>3.80.42.186.KOR.00.000</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
-        <is>
-          <t>Cáp tròn điều khiển cẩu trục có cáp chịu lực - Cáp tròn điều khiển cẩu trục có cáp chịu lực: Mã sản phẩm: 1.5SQx20C 
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Cáp tròn điều khiển cẩu trục có cáp chịu lực</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Cáp tròn điều khiển cẩu trục có cáp chịu lực: Mã sản phẩm: 1.5SQx20C 
 Đường kính: 1.5mm2 /lõi (bao gồm 20 sợi lõi). Vật liệu lõi: Đồng</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Dae Duk/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="G61" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="H61" s="7" t="n">
         <v>909000</v>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="I61" s="7" t="n">
         <v>18180000</v>
       </c>
-      <c r="H61" s="7" t="inlineStr"/>
-      <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="6" t="n">
+      <c r="J61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr"/>
+      <c r="L61" s="7" t="n">
         <v>909000</v>
       </c>
-      <c r="K61" s="6" t="n">
+      <c r="M61" s="7" t="n">
         <v>18180000</v>
       </c>
-      <c r="L61" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="7" t="inlineStr"/>
+      <c r="N61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="6" t="inlineStr"/>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>3.80.42.186.KOR.00.000 | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -3140,37 +4179,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét - Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét</t>
-        </is>
-      </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Cáp thép 6x36 IWRC, đường kính cáp 12mm, loại 3 tấn: 80 mét</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>Uni/ Mỹ</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="E62" s="6" t="n">
+      <c r="G62" s="7" t="n">
         <v>80</v>
       </c>
-      <c r="F62" s="6" t="n">
+      <c r="H62" s="7" t="n">
         <v>202000</v>
       </c>
-      <c r="G62" s="6" t="n">
+      <c r="I62" s="7" t="n">
         <v>16160000</v>
       </c>
-      <c r="H62" s="7" t="inlineStr"/>
-      <c r="I62" s="7" t="inlineStr"/>
-      <c r="J62" s="6" t="n">
+      <c r="J62" s="6" t="inlineStr"/>
+      <c r="K62" s="6" t="inlineStr"/>
+      <c r="L62" s="7" t="n">
         <v>202000</v>
       </c>
-      <c r="K62" s="6" t="n">
+      <c r="M62" s="7" t="n">
         <v>16160000</v>
       </c>
-      <c r="L62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="7" t="inlineStr"/>
+      <c r="N62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="6" t="inlineStr"/>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -3181,39 +4235,54 @@
           <t>2.50.05.003.CHN.00.000</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>Cáp inox 304 
-Kích thước: Ø 3 mm - Cáp inox 304 
 Kích thước: Ø 3 mm</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Cáp inox 304 
+Kích thước: Ø 3 mm</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="E63" s="6" t="n">
+      <c r="G63" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="F63" s="6" t="n">
+      <c r="H63" s="7" t="n">
         <v>37000</v>
       </c>
-      <c r="G63" s="6" t="n">
+      <c r="I63" s="7" t="n">
         <v>2220000</v>
       </c>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="6" t="n">
+      <c r="J63" s="6" t="inlineStr"/>
+      <c r="K63" s="6" t="inlineStr"/>
+      <c r="L63" s="7" t="n">
         <v>37000</v>
       </c>
-      <c r="K63" s="6" t="n">
+      <c r="M63" s="7" t="n">
         <v>2220000</v>
       </c>
-      <c r="L63" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="7" t="inlineStr"/>
+      <c r="N63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="6" t="inlineStr"/>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>2.50.05.003.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -3224,38 +4293,53 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Phe cài trục ngoài cho đường kính 28mm - Phe cài trục ngoài cho đường kính 28mm.
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Phe cài trục ngoài cho đường kính 28mm.
 Vật liệu: Inox 304</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="G64" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="H64" s="7" t="n">
         <v>56000</v>
       </c>
-      <c r="G64" s="6" t="n">
+      <c r="I64" s="7" t="n">
         <v>56000</v>
       </c>
-      <c r="H64" s="7" t="inlineStr"/>
-      <c r="I64" s="7" t="inlineStr"/>
-      <c r="J64" s="6" t="n">
+      <c r="J64" s="6" t="inlineStr"/>
+      <c r="K64" s="6" t="inlineStr"/>
+      <c r="L64" s="7" t="n">
         <v>56000</v>
       </c>
-      <c r="K64" s="6" t="n">
+      <c r="M64" s="7" t="n">
         <v>56000</v>
       </c>
-      <c r="L64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="7" t="inlineStr"/>
+      <c r="N64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="6" t="inlineStr"/>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa Tời điện Tời điện 3 tấn nằm ngoài BSKK theo BBKT 558/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -3266,43 +4350,58 @@
           <t>2.06.60.032.TPE.00.000</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>Thanh ray C
 Loại: CH2201
-Size: 32x30x1.5mm dài 3m - Thanh ray C
+Size: 32x30x1.5mm dài 3m</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>Thanh ray C
 Loại: CH2201
 Size: 32x30x1.5mm dài 3m
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>ITS/ Đài Loan</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>Thanh</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
+      <c r="G65" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="F65" s="6" t="n">
+      <c r="H65" s="7" t="n">
         <v>4520000</v>
       </c>
-      <c r="G65" s="6" t="n">
+      <c r="I65" s="7" t="n">
         <v>63280000</v>
       </c>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="6" t="n">
+      <c r="J65" s="6" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr"/>
+      <c r="L65" s="7" t="n">
         <v>4520000</v>
       </c>
-      <c r="K65" s="6" t="n">
+      <c r="M65" s="7" t="n">
         <v>63280000</v>
       </c>
-      <c r="L65" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="7" t="inlineStr"/>
+      <c r="N65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="6" t="inlineStr"/>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>2.06.60.032.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -3313,43 +4412,58 @@
           <t>2.06.60.038.TPE.00.000</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>Nối ray C
 Loại: CH2230
-Size: 40x38x3mm, dài 100mm - Nối ray C
+Size: 40x38x3mm, dài 100mm</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>Nối ray C
 Loại: CH2230
 Size: 40x38x3mm, dài 100mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>ITS/ Đài Loan</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E66" s="6" t="n">
+      <c r="G66" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="F66" s="6" t="n">
+      <c r="H66" s="7" t="n">
         <v>1120000</v>
       </c>
-      <c r="G66" s="6" t="n">
+      <c r="I66" s="7" t="n">
         <v>13440000</v>
       </c>
-      <c r="H66" s="7" t="inlineStr"/>
-      <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="6" t="n">
+      <c r="J66" s="6" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr"/>
+      <c r="L66" s="7" t="n">
         <v>1120000</v>
       </c>
-      <c r="K66" s="6" t="n">
+      <c r="M66" s="7" t="n">
         <v>13440000</v>
       </c>
-      <c r="L66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="7" t="inlineStr"/>
+      <c r="N66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="6" t="inlineStr"/>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>2.06.60.038.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -3360,43 +4474,58 @@
           <t>2.35.16.032.TPE.00.000</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>Giữ ray
 Loại: CH2240
-Size: 80x25x3mm - Giữ ray
+Size: 80x25x3mm</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>Giữ ray
 Loại: CH2240
 Size: 80x25x3mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>ITS/ Đài Loan</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E67" s="6" t="n">
+      <c r="G67" s="7" t="n">
         <v>51</v>
       </c>
-      <c r="F67" s="6" t="n">
+      <c r="H67" s="7" t="n">
         <v>905000</v>
       </c>
-      <c r="G67" s="6" t="n">
+      <c r="I67" s="7" t="n">
         <v>46155000</v>
       </c>
-      <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="6" t="n">
+      <c r="J67" s="6" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr"/>
+      <c r="L67" s="7" t="n">
         <v>905000</v>
       </c>
-      <c r="K67" s="6" t="n">
+      <c r="M67" s="7" t="n">
         <v>46155000</v>
       </c>
-      <c r="L67" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="7" t="inlineStr"/>
+      <c r="N67" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="6" t="inlineStr"/>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>2.35.16.032.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -3407,41 +4536,56 @@
           <t>2.06.60.078.TPE.00.000</t>
         </is>
       </c>
-      <c r="C68" s="5" t="inlineStr">
+      <c r="C68" s="6" t="inlineStr">
         <is>
           <t>Con lăn dẫn cáp
-Loại: CH2220-1 78x85mm - Con lăn dẫn cáp
+Loại: CH2220-1 78x85mm</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Con lăn dẫn cáp
 Loại: CH2220-1 78x85mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>ITS/ Đài Loan</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n">
+      <c r="G68" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="F68" s="6" t="n">
+      <c r="H68" s="7" t="n">
         <v>2710000</v>
       </c>
-      <c r="G68" s="6" t="n">
+      <c r="I68" s="7" t="n">
         <v>86720000</v>
       </c>
-      <c r="H68" s="7" t="inlineStr"/>
-      <c r="I68" s="7" t="inlineStr"/>
-      <c r="J68" s="6" t="n">
+      <c r="J68" s="6" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr"/>
+      <c r="L68" s="7" t="n">
         <v>2710000</v>
       </c>
-      <c r="K68" s="6" t="n">
+      <c r="M68" s="7" t="n">
         <v>86720000</v>
       </c>
-      <c r="L68" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="7" t="inlineStr"/>
+      <c r="N68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="6" t="inlineStr"/>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>2.06.60.078.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="n">
@@ -3452,41 +4596,56 @@
           <t>2.06.60.085.TPE.00.000</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>Con lăn dẫn đầu
-Loại: CH2250 78x80 mm - Con lăn dẫn đầu
+Loại: CH2250 78x80 mm</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Con lăn dẫn đầu
 Loại: CH2250 78x80 mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="D69" s="4" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>ITS/ Đài Loan</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E69" s="6" t="n">
+      <c r="G69" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F69" s="6" t="n">
+      <c r="H69" s="7" t="n">
         <v>980000</v>
       </c>
-      <c r="G69" s="6" t="n">
+      <c r="I69" s="7" t="n">
         <v>1960000</v>
       </c>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
-      <c r="J69" s="6" t="n">
+      <c r="J69" s="6" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr"/>
+      <c r="L69" s="7" t="n">
         <v>980000</v>
       </c>
-      <c r="K69" s="6" t="n">
+      <c r="M69" s="7" t="n">
         <v>1960000</v>
       </c>
-      <c r="L69" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="7" t="inlineStr"/>
+      <c r="N69" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="6" t="inlineStr"/>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>2.06.60.085.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="n">
@@ -3497,43 +4656,58 @@
           <t>2.06.60.080.TPE.00.000</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>Kẹp cố định đầu ray
 Loại: CH2260
-Size: 80x51x3mm - Kẹp cố định đầu ray
+Size: 80x51x3mm</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Kẹp cố định đầu ray
 Loại: CH2260
 Size: 80x51x3mm
 Vật liệu: Inox 304
 Hãng: ITS Đài loan</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>ITS/ Đài Loan</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E70" s="6" t="n">
+      <c r="G70" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F70" s="6" t="n">
+      <c r="H70" s="7" t="n">
         <v>2254000</v>
       </c>
-      <c r="G70" s="6" t="n">
+      <c r="I70" s="7" t="n">
         <v>4508000</v>
       </c>
-      <c r="H70" s="7" t="inlineStr"/>
-      <c r="I70" s="7" t="inlineStr"/>
-      <c r="J70" s="6" t="n">
+      <c r="J70" s="6" t="inlineStr"/>
+      <c r="K70" s="6" t="inlineStr"/>
+      <c r="L70" s="7" t="n">
         <v>2254000</v>
       </c>
-      <c r="K70" s="6" t="n">
+      <c r="M70" s="7" t="n">
         <v>4508000</v>
       </c>
-      <c r="L70" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="7" t="inlineStr"/>
+      <c r="N70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="6" t="inlineStr"/>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>2.06.60.080.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="n">
@@ -3544,41 +4718,56 @@
           <t>4.82.72.013.VIE.00.000</t>
         </is>
       </c>
-      <c r="C71" s="5" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Ống nối cáp điện:
-Model: SL16 - Ống nối cáp điện:
+Model: SL16</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Ống nối cáp điện:
 Model: SL16
 Chất liệu Đồng thau
 Tiết diện cáp sử dụng 16 mm2</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E71" s="6" t="n">
+      <c r="G71" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F71" s="6" t="n">
+      <c r="H71" s="7" t="n">
         <v>12000</v>
       </c>
-      <c r="G71" s="6" t="n">
+      <c r="I71" s="7" t="n">
         <v>192000</v>
       </c>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr"/>
-      <c r="J71" s="6" t="n">
+      <c r="J71" s="6" t="inlineStr"/>
+      <c r="K71" s="6" t="inlineStr"/>
+      <c r="L71" s="7" t="n">
         <v>12000</v>
       </c>
-      <c r="K71" s="6" t="n">
+      <c r="M71" s="7" t="n">
         <v>192000</v>
       </c>
-      <c r="L71" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="7" t="inlineStr"/>
+      <c r="N71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="6" t="inlineStr"/>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>4.82.72.013.VIE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -3589,11 +4778,16 @@
           <t>3.15.44.076.CHN.00.000</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
-Ruột mềm - Cáp điện dẹt cho cầu trục
+Ruột mềm</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Cáp điện dẹt cho cầu trục
 Quy cách: 16mm2 x 4C
 Ruột mềm
 Điện áp: 450/750V
@@ -3601,32 +4795,42 @@
 NSX: Imatek</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>Imatek/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="E72" s="6" t="n">
+      <c r="G72" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="F72" s="6" t="n">
+      <c r="H72" s="7" t="n">
         <v>711000</v>
       </c>
-      <c r="G72" s="6" t="n">
+      <c r="I72" s="7" t="n">
         <v>35550000</v>
       </c>
-      <c r="H72" s="7" t="inlineStr"/>
-      <c r="I72" s="7" t="inlineStr"/>
-      <c r="J72" s="6" t="n">
+      <c r="J72" s="6" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr"/>
+      <c r="L72" s="7" t="n">
         <v>711000</v>
       </c>
-      <c r="K72" s="6" t="n">
+      <c r="M72" s="7" t="n">
         <v>35550000</v>
       </c>
-      <c r="L72" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" s="7" t="inlineStr"/>
+      <c r="N72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="6" t="inlineStr"/>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>3.15.44.076.CHN.00.000 | Sửa chữa Tời điện 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
@@ -3637,39 +4841,54 @@
           <t>3.20.22.003.TPE.00.000</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>Khóa cáp 
-Dùng cho cáp: 3mm - Khóa cáp 
 Dùng cho cáp: 3mm</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Khóa cáp 
+Dùng cho cáp: 3mm</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E73" s="6" t="n">
+      <c r="G73" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="F73" s="6" t="n">
+      <c r="H73" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="G73" s="6" t="n">
+      <c r="I73" s="7" t="n">
         <v>1100000</v>
       </c>
-      <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="7" t="inlineStr"/>
-      <c r="J73" s="6" t="n">
+      <c r="J73" s="6" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr"/>
+      <c r="L73" s="7" t="n">
         <v>20000</v>
       </c>
-      <c r="K73" s="6" t="n">
+      <c r="M73" s="7" t="n">
         <v>1100000</v>
       </c>
-      <c r="L73" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" s="7" t="inlineStr"/>
+      <c r="N73" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="6" t="inlineStr"/>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>3.20.22.003.TPE.00.000 | Sửa chữa Tời điện Tời điện 1 tấn và 5 tấn bộ GGH theo BBKT 612/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
@@ -3680,40 +4899,55 @@
           <t>3.34.20.130.CHN.99.000</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>Pendant control station (Tay bấm điều khiển tời điện): 
-- Type: XAC-A6713 - Pendant control station (Tay bấm điều khiển tời điện): 
+- Type: XAC-A6713</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Pendant control station (Tay bấm điều khiển tời điện): 
 - Type: XAC-A6713
 Control station composition: 06, push buttons + 01 emergency stop</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="E74" s="5" t="inlineStr">
+        <is>
+          <t>Schnerder/ Czech Republic</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n">
+      <c r="G74" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F74" s="6" t="n">
+      <c r="H74" s="7" t="n">
         <v>7406000</v>
       </c>
-      <c r="G74" s="6" t="n">
+      <c r="I74" s="7" t="n">
         <v>7406000</v>
       </c>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="7" t="inlineStr"/>
-      <c r="J74" s="6" t="n">
+      <c r="J74" s="6" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr"/>
+      <c r="L74" s="7" t="n">
         <v>7406000</v>
       </c>
-      <c r="K74" s="6" t="n">
+      <c r="M74" s="7" t="n">
         <v>7406000</v>
       </c>
-      <c r="L74" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="7" t="inlineStr"/>
+      <c r="N74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O74" s="6" t="inlineStr"/>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>3.34.20.130.CHN.99.000 | Sửa chữa Tời điện Tời điện 3 tấn máy nén khí turbine theo BBKT 624/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
@@ -3724,39 +4958,54 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
-        <is>
-          <t>Lưỡi gà móc cẩu 7 tấn - Lưỡi gà móc cẩu 7 tấn:
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Lưỡi gà móc cẩu 7 tấn:
  + Kích thước: 60 x 175x 3mm
  + Vật liệu: thép</t>
         </is>
       </c>
-      <c r="D75" s="4" t="inlineStr">
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E75" s="6" t="n">
+      <c r="G75" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="6" t="n">
+      <c r="H75" s="7" t="n">
         <v>656000</v>
       </c>
-      <c r="G75" s="6" t="n">
+      <c r="I75" s="7" t="n">
         <v>656000</v>
       </c>
-      <c r="H75" s="7" t="inlineStr"/>
-      <c r="I75" s="7" t="inlineStr"/>
-      <c r="J75" s="6" t="n">
+      <c r="J75" s="6" t="inlineStr"/>
+      <c r="K75" s="6" t="inlineStr"/>
+      <c r="L75" s="7" t="n">
         <v>656000</v>
       </c>
-      <c r="K75" s="6" t="n">
+      <c r="M75" s="7" t="n">
         <v>656000</v>
       </c>
-      <c r="L75" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" s="7" t="inlineStr"/>
+      <c r="N75" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="6" t="inlineStr"/>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
@@ -3767,37 +5016,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
-        <is>
-          <t>Sơn dầu Jotun chống sét Green 437 - Sơn dầu Jotun chống sét Green 437</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Sơn dầu Jotun chống sét Green 437</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Sơn dầu Jotun chống sét Green 437</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
+        <is>
+          <t>Kungho/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
         <is>
           <t>Lít</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n">
+      <c r="G76" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F76" s="6" t="n">
+      <c r="H76" s="7" t="n">
         <v>625000</v>
       </c>
-      <c r="G76" s="6" t="n">
+      <c r="I76" s="7" t="n">
         <v>12500000</v>
       </c>
-      <c r="H76" s="7" t="inlineStr"/>
-      <c r="I76" s="7" t="inlineStr"/>
-      <c r="J76" s="6" t="n">
+      <c r="J76" s="6" t="inlineStr"/>
+      <c r="K76" s="6" t="inlineStr"/>
+      <c r="L76" s="7" t="n">
         <v>625000</v>
       </c>
-      <c r="K76" s="6" t="n">
+      <c r="M76" s="7" t="n">
         <v>12500000</v>
       </c>
-      <c r="L76" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" s="7" t="inlineStr"/>
+      <c r="N76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="6" t="inlineStr"/>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã | Sửa chữa tời điên Cầu trục 7 tấn lưới quay rác trạm bơm tuần hoàn theo BBKT 432/2026/VH-VT4 | Chưa đề xuất trong KHSXKD, không tồn kho vật tư thay thế tương đương</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
@@ -3808,40 +5072,55 @@
           <t>3.82.63.103.LTU.00.000</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS 01 - FPN - Đế gắn module IO:
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS 01 - FPN</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO:
 - Hãng: ABB
 - Mã: HBS 01 - FPN
-- PR (Product Revision): J hoặc mới hơn</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
+- PR (Product Revision): M</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>ABB/ Lithuania</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E77" s="6" t="n">
+      <c r="G77" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="F77" s="6" t="n">
+      <c r="H77" s="7" t="n">
         <v>21120000</v>
       </c>
-      <c r="G77" s="6" t="n">
+      <c r="I77" s="7" t="n">
         <v>633600000</v>
       </c>
-      <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="6" t="n">
+      <c r="J77" s="6" t="inlineStr"/>
+      <c r="K77" s="6" t="inlineStr"/>
+      <c r="L77" s="7" t="n">
         <v>21120000</v>
       </c>
-      <c r="K77" s="6" t="n">
+      <c r="M77" s="7" t="n">
         <v>633600000</v>
       </c>
-      <c r="L77" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" s="7" t="inlineStr"/>
+      <c r="N77" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="6" t="inlineStr"/>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>3.82.63.103.LTU.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung  | Vật tư không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -3852,40 +5131,55 @@
           <t>3.94.00.808.MLT.00.000</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS01-FPH - Đế gắn module IO:
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS01-FPH</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO:
 - Hãng: ABB
 - Mã: HBS 01 - FPH
-- PR (Product Revision): J hoặc mới hơn</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
+- PR (Product Revision): M</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>ABB/ Lithuania</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n">
+      <c r="G78" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="F78" s="6" t="n">
+      <c r="H78" s="7" t="n">
         <v>21120000</v>
       </c>
-      <c r="G78" s="6" t="n">
+      <c r="I78" s="7" t="n">
         <v>549120000</v>
       </c>
-      <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="7" t="inlineStr"/>
-      <c r="J78" s="6" t="n">
+      <c r="J78" s="6" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr"/>
+      <c r="L78" s="7" t="n">
         <v>21120000</v>
       </c>
-      <c r="K78" s="6" t="n">
+      <c r="M78" s="7" t="n">
         <v>549120000</v>
       </c>
-      <c r="L78" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="7" t="inlineStr"/>
+      <c r="N78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="6" t="inlineStr"/>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>3.94.00.808.MLT.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung | Vật tư không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
@@ -3896,40 +5190,55 @@
           <t>3.82.63.102.LTU.00.000</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>Đế gắn module IO HBS01-EPD - Đế gắn module IO:
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO HBS01-EPD</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Đế gắn module IO:
 - Hãng: ABB
 - Mã: HBS 01 - EPD
-- PR (Product Revision): J hoặc mới hơn</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
+- PR (Product Revision): M</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
+        <is>
+          <t>ABB/ Lithuania</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E79" s="6" t="n">
+      <c r="G79" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F79" s="6" t="n">
+      <c r="H79" s="7" t="n">
+        <v>18350000</v>
+      </c>
+      <c r="I79" s="7" t="n">
+        <v>183500000</v>
+      </c>
+      <c r="J79" s="6" t="inlineStr"/>
+      <c r="K79" s="6" t="inlineStr"/>
+      <c r="L79" s="7" t="n">
         <v>21120000</v>
       </c>
-      <c r="G79" s="6" t="n">
+      <c r="M79" s="7" t="n">
         <v>211200000</v>
       </c>
-      <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="6" t="n">
-        <v>21120000</v>
-      </c>
-      <c r="K79" s="6" t="n">
-        <v>211200000</v>
-      </c>
-      <c r="L79" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" s="7" t="inlineStr"/>
+      <c r="N79" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O79" s="6" t="inlineStr"/>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>3.82.63.102.LTU.00.000 | Dự phòng thay thế cho các đế module IO hệ thống DCS ABB tổ máy S1, S2, S3 và COM suy giảm điện dung | Vật tư không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
@@ -3940,37 +5249,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
-        <is>
-          <t>Bạc đạn RN206E - Bạc đạn RN206E</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Bạc đạn RN206E</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Bạc đạn RN206E</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="inlineStr">
+        <is>
+          <t>SKF/ Đức</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E80" s="6" t="n">
+      <c r="G80" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F80" s="6" t="n">
+      <c r="H80" s="7" t="n">
         <v>1261000</v>
       </c>
-      <c r="G80" s="6" t="n">
+      <c r="I80" s="7" t="n">
         <v>1261000</v>
       </c>
-      <c r="H80" s="7" t="inlineStr"/>
-      <c r="I80" s="7" t="inlineStr"/>
-      <c r="J80" s="6" t="n">
+      <c r="J80" s="6" t="inlineStr"/>
+      <c r="K80" s="6" t="inlineStr"/>
+      <c r="L80" s="7" t="n">
         <v>1261000</v>
       </c>
-      <c r="K80" s="6" t="n">
+      <c r="M80" s="7" t="n">
         <v>1261000</v>
       </c>
-      <c r="L80" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" s="7" t="inlineStr"/>
+      <c r="N80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="6" t="inlineStr"/>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã ERP | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
@@ -3981,37 +5305,52 @@
           <t>5.01.07.302.FRA.00.000</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
-        <is>
-          <t>Bạc đạn 6302 - Bạc đạn 6302</t>
-        </is>
-      </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6302</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>SKF/ Pháp</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E81" s="6" t="n">
+      <c r="G81" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F81" s="6" t="n">
+      <c r="H81" s="7" t="n">
         <v>158000</v>
       </c>
-      <c r="G81" s="6" t="n">
+      <c r="I81" s="7" t="n">
         <v>316000</v>
       </c>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="6" t="n">
+      <c r="J81" s="6" t="inlineStr"/>
+      <c r="K81" s="6" t="inlineStr"/>
+      <c r="L81" s="7" t="n">
         <v>158000</v>
       </c>
-      <c r="K81" s="6" t="n">
+      <c r="M81" s="7" t="n">
         <v>316000</v>
       </c>
-      <c r="L81" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" s="7" t="inlineStr"/>
+      <c r="N81" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O81" s="6" t="inlineStr"/>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>5.01.07.302.FRA.00.000 | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
@@ -4022,37 +5361,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>Bạc đạn 6208 - Bạc đạn 6208</t>
-        </is>
-      </c>
-      <c r="D82" s="4" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6208</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Bạc đạn 6208</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
+        <is>
+          <t>SKF/ Pháp</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
         <is>
           <t>Vòng</t>
         </is>
       </c>
-      <c r="E82" s="6" t="n">
+      <c r="G82" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F82" s="6" t="n">
+      <c r="H82" s="7" t="n">
         <v>444000</v>
       </c>
-      <c r="G82" s="6" t="n">
+      <c r="I82" s="7" t="n">
         <v>1776000</v>
       </c>
-      <c r="H82" s="7" t="inlineStr"/>
-      <c r="I82" s="7" t="inlineStr"/>
-      <c r="J82" s="6" t="n">
+      <c r="J82" s="6" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr"/>
+      <c r="L82" s="7" t="n">
         <v>444000</v>
       </c>
-      <c r="K82" s="6" t="n">
+      <c r="M82" s="7" t="n">
         <v>1776000</v>
       </c>
-      <c r="L82" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" s="7" t="inlineStr"/>
+      <c r="N82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="6" t="inlineStr"/>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã ERP | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
@@ -4063,11 +5417,16 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
 + Cycloidal Gear Reducer Type: 
-XLD3-59-1.1KW - Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
+XLD3-59-1.1KW</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Đĩa dao động - Cycloidal disc (1 bộ gồm 2 cái)
 + Cycloidal Gear Reducer Type: 
 XLD3-59-1.1KW
 + Input Power: 1.1 KW
@@ -4075,32 +5434,42 @@
 + Nhà sản xuất: JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>JIANGSU TAILONG DECELERATOR MACHINERY CO.,LTD/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E83" s="6" t="n">
+      <c r="G83" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="6" t="n">
+      <c r="H83" s="7" t="n">
         <v>58240000</v>
       </c>
-      <c r="G83" s="6" t="n">
+      <c r="I83" s="7" t="n">
         <v>58240000</v>
       </c>
-      <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
-      <c r="J83" s="6" t="n">
+      <c r="J83" s="6" t="inlineStr"/>
+      <c r="K83" s="6" t="inlineStr"/>
+      <c r="L83" s="7" t="n">
         <v>58240000</v>
       </c>
-      <c r="K83" s="6" t="n">
+      <c r="M83" s="7" t="n">
         <v>58240000</v>
       </c>
-      <c r="L83" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="7" t="inlineStr"/>
+      <c r="N83" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="6" t="inlineStr"/>
+      <c r="P83" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã ERP | Sửa chữa theo BBKT 971/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
@@ -4111,39 +5480,54 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>Túi lọc bụi tay áo, KT: D160x3000(mm), chất liệu: vải Polyester - Túi lọc bụi (thu bụi cho tháp 09 loại JJWM-300A), 
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Túi lọc bụi tay áo, KT: D160x3000(mm), chất liệu: vải Polyester</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>Túi lọc bụi (thu bụi cho tháp 09 loại JJWM-300A), 
 - KT: ɸ160x3000(mm);
 - Chất liệu: Vải polyester.</t>
         </is>
       </c>
-      <c r="D84" s="4" t="inlineStr">
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>Tân Thanh/ Việt Nam</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="G84" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="H84" s="7" t="n">
         <v>1680000</v>
       </c>
-      <c r="G84" s="6" t="n">
+      <c r="I84" s="7" t="n">
         <v>336000000</v>
       </c>
-      <c r="H84" s="7" t="inlineStr"/>
-      <c r="I84" s="7" t="inlineStr"/>
-      <c r="J84" s="6" t="n">
+      <c r="J84" s="6" t="inlineStr"/>
+      <c r="K84" s="6" t="inlineStr"/>
+      <c r="L84" s="7" t="n">
         <v>1680000</v>
       </c>
-      <c r="K84" s="6" t="n">
+      <c r="M84" s="7" t="n">
         <v>336000000</v>
       </c>
-      <c r="L84" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="7" t="inlineStr"/>
+      <c r="N84" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="6" t="inlineStr"/>
+      <c r="P84" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã ERP | Sửa chữa theo BBKT 831/2026/NL-VT4  | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
@@ -4154,9 +5538,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
-        <is>
-          <t>Armor ring Vành hướng gió máy nghiền than - Armor ring 
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Armor ring Vành hướng gió máy nghiền than</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Armor ring 
 Vành hướng gió
 Bao gồm 16 chi tiết (tấm)
 Chế tạo bằng thép Kalmetall W100/Kalenborn
@@ -4168,32 +5557,42 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>ML/ Ba Lan</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E85" s="6" t="n">
+      <c r="G85" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F85" s="6" t="n">
+      <c r="H85" s="7" t="n">
         <v>738496000</v>
       </c>
-      <c r="G85" s="6" t="n">
+      <c r="I85" s="7" t="n">
         <v>1476992000</v>
       </c>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="6" t="n">
+      <c r="J85" s="6" t="inlineStr"/>
+      <c r="K85" s="6" t="inlineStr"/>
+      <c r="L85" s="7" t="n">
         <v>738496000</v>
       </c>
-      <c r="K85" s="6" t="n">
+      <c r="M85" s="7" t="n">
         <v>1476992000</v>
       </c>
-      <c r="L85" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="7" t="inlineStr"/>
+      <c r="N85" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="6" t="inlineStr"/>
+      <c r="P85" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay thế mới các chi tiết của vành chặn than lining ring, tấm viền đáy thùng nghiền các máy nghiền bị mài mòn nặng | Vật tư đã chuẩn hóa ERP, không tồn kho. Vật tư chưa đề xuất mua sắm trong KHSXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
@@ -4204,9 +5603,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
-        <is>
-          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than - Lining Plate (Compound Armour Plate)
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>Lining Plate (Compound Armour Plate)
 Tấm lót thân máy nghiền
 Bao gồm 106 chi tiết (tấm)
 Chế tạo bằng thép Kalmetall W100/Kalenborn
@@ -4219,32 +5623,42 @@
 - Chống mài mòn theo ASTM G65: 0,0060 mm3/m</t>
         </is>
       </c>
-      <c r="D86" s="4" t="inlineStr">
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>ML/ Ba Lan</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E86" s="6" t="n">
+      <c r="G86" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F86" s="6" t="n">
+      <c r="H86" s="7" t="n">
         <v>2618304000</v>
       </c>
-      <c r="G86" s="6" t="n">
+      <c r="I86" s="7" t="n">
         <v>5236608000</v>
       </c>
-      <c r="H86" s="7" t="inlineStr"/>
-      <c r="I86" s="7" t="inlineStr"/>
-      <c r="J86" s="6" t="n">
+      <c r="J86" s="6" t="inlineStr"/>
+      <c r="K86" s="6" t="inlineStr"/>
+      <c r="L86" s="7" t="n">
         <v>2618304000</v>
       </c>
-      <c r="K86" s="6" t="n">
+      <c r="M86" s="7" t="n">
         <v>5236608000</v>
       </c>
-      <c r="L86" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="7" t="inlineStr"/>
+      <c r="N86" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="6" t="inlineStr"/>
+      <c r="P86" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay thế mới tấm lining ở vách thùng nghiền, phía sau con lăn, cửa manhole các máy nghiền bị mài mòn nặng | Vật tư đã chuẩn hóa ERP, không tồn kho. Vật tư chưa đề xuất mua sắm trong KHSXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
@@ -4255,39 +5669,54 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>Keo phủ chống mài mòn Kalpoxy-150 - Wear Resistant Mortar (Keo chống mài mòn)
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Keo phủ chống mài mòn Kalpoxy-150</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Wear Resistant Mortar (Keo chống mài mòn)
 Keo phủ chống mài mòn Kalpoxy-150/Kalenborn 
 (01 cặp bao gồm hardener + Resin)</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Kalenborn/ Đức</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
         <is>
           <t>Cặp</t>
         </is>
       </c>
-      <c r="E87" s="6" t="n">
+      <c r="G87" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F87" s="6" t="n">
+      <c r="H87" s="7" t="n">
         <v>16320000</v>
       </c>
-      <c r="G87" s="6" t="n">
+      <c r="I87" s="7" t="n">
         <v>326400000</v>
       </c>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="6" t="n">
+      <c r="J87" s="6" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr"/>
+      <c r="L87" s="7" t="n">
         <v>16320000</v>
       </c>
-      <c r="K87" s="6" t="n">
+      <c r="M87" s="7" t="n">
         <v>326400000</v>
       </c>
-      <c r="L87" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="7" t="inlineStr"/>
+      <c r="N87" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="6" t="inlineStr"/>
+      <c r="P87" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Dán các tấm lining plate khi thay thế | Vật tư đã chuẩn hóa ERP, không tồn kho. Vật tư chưa đề xuất mua sắm trong KHSXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
@@ -4298,37 +5727,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>Nút van/main plug pos 04-01; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02,19-245-01-01/02/03/04 - Nút van/main plug pos 04-01; material: 440C SS+HT; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="D88" s="4" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Nút van/main plug pos 04-01; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02,19-245-01-01/02/03/04</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>Nút van/main plug pos 04-01; material: 440C SS+HT; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>Unicon/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E88" s="6" t="n">
+      <c r="G88" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F88" s="6" t="n">
+      <c r="H88" s="7" t="n">
         <v>661500000</v>
       </c>
-      <c r="G88" s="6" t="n">
+      <c r="I88" s="7" t="n">
         <v>3969000000</v>
       </c>
-      <c r="H88" s="7" t="inlineStr"/>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="6" t="n">
+      <c r="J88" s="6" t="inlineStr"/>
+      <c r="K88" s="6" t="inlineStr"/>
+      <c r="L88" s="7" t="n">
         <v>661500000</v>
       </c>
-      <c r="K88" s="6" t="n">
+      <c r="M88" s="7" t="n">
         <v>3969000000</v>
       </c>
-      <c r="L88" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="7" t="inlineStr"/>
+      <c r="N88" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="6" t="inlineStr"/>
+      <c r="P88" s="6" t="inlineStr">
+        <is>
+          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van và mã bản vẽ cho vật tư tại mục 1 YCVT số 607/KTAT và mục 11 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
@@ -4339,37 +5783,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Lò xo đĩa van/Disc Spring pos 04-02; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04 - Lò xo đĩa van /Disc Spring pos 04-02; material: Inconel 718;  sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Lò xo đĩa van/Disc Spring pos 04-02; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Lò xo đĩa van /Disc Spring pos 04-02; material: Inconel 718;  sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Unicon/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E89" s="6" t="n">
+      <c r="G89" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F89" s="6" t="n">
+      <c r="H89" s="7" t="n">
         <v>264600000</v>
       </c>
-      <c r="G89" s="6" t="n">
+      <c r="I89" s="7" t="n">
         <v>1587600000</v>
       </c>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="6" t="n">
+      <c r="J89" s="6" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr"/>
+      <c r="L89" s="7" t="n">
         <v>264600000</v>
       </c>
-      <c r="K89" s="6" t="n">
+      <c r="M89" s="7" t="n">
         <v>1587600000</v>
       </c>
-      <c r="L89" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="7" t="inlineStr"/>
+      <c r="N89" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="6" t="inlineStr"/>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van và mã bản vẽ cho vật tư tại mục 2 YCVT số 607/KTAT và mục 12 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
@@ -4380,37 +5839,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>Nắp lò xo đĩa van/ Spring cap pos 04-03; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04 - Nắp lò xo đĩa van / Spring cap pos 04-03; material: 410 SS; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="D90" s="4" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Nắp lò xo đĩa van/ Spring cap pos 04-03; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>Nắp lò xo đĩa van / Spring cap pos 04-03; material: 410 SS; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>Unicon/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E90" s="6" t="n">
+      <c r="G90" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F90" s="6" t="n">
+      <c r="H90" s="7" t="n">
         <v>220500000</v>
       </c>
-      <c r="G90" s="6" t="n">
+      <c r="I90" s="7" t="n">
         <v>1323000000</v>
       </c>
-      <c r="H90" s="7" t="inlineStr"/>
-      <c r="I90" s="7" t="inlineStr"/>
-      <c r="J90" s="6" t="n">
+      <c r="J90" s="6" t="inlineStr"/>
+      <c r="K90" s="6" t="inlineStr"/>
+      <c r="L90" s="7" t="n">
         <v>220500000</v>
       </c>
-      <c r="K90" s="6" t="n">
+      <c r="M90" s="7" t="n">
         <v>1323000000</v>
       </c>
-      <c r="L90" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="7" t="inlineStr"/>
+      <c r="N90" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="6" t="inlineStr"/>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van và mã bản vẽ cho vật tư tại mục 3 YCVT số 607/KTAT và mục 13 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
@@ -4421,37 +5895,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Lồng đế van/seat basket pos 03; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04 - Lồng đế van/ seat basket pos 03; material: 316SS; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Lồng đế van/seat basket pos 03; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Lồng đế van/ seat basket pos 03; material: 316SS; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Unicon/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E91" s="6" t="n">
+      <c r="G91" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F91" s="6" t="n">
+      <c r="H91" s="7" t="n">
         <v>551250000</v>
       </c>
-      <c r="G91" s="6" t="n">
+      <c r="I91" s="7" t="n">
         <v>3307500000</v>
       </c>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="7" t="inlineStr"/>
-      <c r="J91" s="6" t="n">
+      <c r="J91" s="6" t="inlineStr"/>
+      <c r="K91" s="6" t="inlineStr"/>
+      <c r="L91" s="7" t="n">
         <v>551250000</v>
       </c>
-      <c r="K91" s="6" t="n">
+      <c r="M91" s="7" t="n">
         <v>3307500000</v>
       </c>
-      <c r="L91" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="7" t="inlineStr"/>
+      <c r="N91" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="6" t="inlineStr"/>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van và mã bản vẽ cho vật tư tại mục 4 của YCVT số 607/KTAT và mục 14 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
@@ -4462,37 +5951,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>Trục ty van/ Stem pos 08; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04 - Trục ty van / Stem pos 08; material: Inconel 718; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
-        </is>
-      </c>
-      <c r="D92" s="4" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Trục ty van/ Stem pos 08; sử dụng cho van tái tuần hoàn BFPT A/B; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>Trục ty van / Stem pos 08; material: Inconel 718; sử dụng cho van tái tuần hoàn BFPT A/B; model valve V200SER; class 2500#; serial No: 19-245-02-01/02, 19-245-01-01/02/03/04; Dw no: VT4/VT4E-YR05-P0/P3ZEN-150005; NSX: Unicon/tương đương</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
+        <is>
+          <t>Unicon/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E92" s="6" t="n">
+      <c r="G92" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F92" s="6" t="n">
+      <c r="H92" s="7" t="n">
         <v>351775000</v>
       </c>
-      <c r="G92" s="6" t="n">
+      <c r="I92" s="7" t="n">
         <v>2110650000</v>
       </c>
-      <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="7" t="inlineStr"/>
-      <c r="J92" s="6" t="n">
+      <c r="J92" s="6" t="inlineStr"/>
+      <c r="K92" s="6" t="inlineStr"/>
+      <c r="L92" s="7" t="n">
         <v>351775000</v>
       </c>
-      <c r="K92" s="6" t="n">
+      <c r="M92" s="7" t="n">
         <v>2110650000</v>
       </c>
-      <c r="L92" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="7" t="inlineStr"/>
+      <c r="N92" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="6" t="inlineStr"/>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>Chưa mua sắm | Vật tư dùng để thay thế các chi tiết ty van, đế van bị khuyết vật liệu gây rò rỉ bên trong van tái tuần hoàn BFPT các tổ máy | Cập nhật số serial van,mã bản vẽ, điều chỉnh vật liệu theo bản vẽ mới nhất cho vật tư tại mục 15 của YCVT số 2039/KTATVật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n">
@@ -4503,38 +6007,53 @@
           <t>3.96.13.309.KOR.00.000</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613 - Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>Công tắc báo tốc độ băng tải SDCC Speed switch Model: SSM-613
 NSX: Shinsung</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Shinsung/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
         <is>
           <t>Cái</t>
         </is>
       </c>
-      <c r="E93" s="6" t="n">
+      <c r="G93" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="F93" s="6" t="n">
+      <c r="H93" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="G93" s="6" t="n">
+      <c r="I93" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
-      <c r="J93" s="6" t="n">
+      <c r="J93" s="6" t="inlineStr"/>
+      <c r="K93" s="6" t="inlineStr"/>
+      <c r="L93" s="7" t="n">
         <v>30000000</v>
       </c>
-      <c r="K93" s="6" t="n">
+      <c r="M93" s="7" t="n">
         <v>90000000</v>
       </c>
-      <c r="L93" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" s="7" t="inlineStr"/>
+      <c r="N93" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="6" t="inlineStr"/>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>3.96.13.309.KOR.00.000 | BBKT- 1190/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến đo tốc độ xích cào DCC tổ máy S2 báo lỗi. BBKT- 1284/2026/VH-VT4, 1285/2026/VH-VT4_ Kiểm tra, khắc phục cảm biến đo tốc độ xích cào thuyền xỉ SDCC tổ máy S2, S3 báo lỗi.  Vật tư không có trong KH SXKD 2026. | Mua sắm thay thế hết tồn kho thiết bị giám sát quan trọng.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n">
@@ -4545,9 +6064,14 @@
           <t>3.96.11.015.SIN.00.000</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4 - Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4 
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>Cảm biến áp suất (Pressure transmitter) Model: 2051CG2A02A1AS5M5D4T1Q4 
 Output Hart: 4-20mA 
 Supply: 10.5 – 42.4 VDC 
 CAL: 0 to 150 mbarg 
@@ -4555,32 +6079,42 @@
 NSX: Rosemount</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>Rosemount/ Singapore</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E94" s="6" t="n">
+      <c r="G94" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F94" s="6" t="n">
+      <c r="H94" s="7" t="n">
         <v>195000000</v>
       </c>
-      <c r="G94" s="6" t="n">
+      <c r="I94" s="7" t="n">
         <v>195000000</v>
       </c>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="7" t="inlineStr"/>
-      <c r="J94" s="6" t="n">
+      <c r="J94" s="6" t="inlineStr"/>
+      <c r="K94" s="6" t="inlineStr"/>
+      <c r="L94" s="7" t="n">
         <v>195000000</v>
       </c>
-      <c r="K94" s="6" t="n">
+      <c r="M94" s="7" t="n">
         <v>195000000</v>
       </c>
-      <c r="L94" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="7" t="inlineStr"/>
+      <c r="N94" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="6" t="inlineStr"/>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>3.96.11.015.SIN.00.000 | BBKT- 1252/2026/VH-VT4_ Kiểm tra, khắc phục bộ chuyển đổi tín hiệu đo áp suất gió vào MN A S3 báo lỗi. | Vật tư không có trong KH SXKD 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n">
@@ -4591,37 +6125,52 @@
           <t>5.08.78.858.CHN.00.000</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5) - Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5)</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5)</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>Conveyor belts ST800 B1800X3.5 (5+5) / Băng tải cho hệ thống nhiên liệu ST800 B1800X3.5 (5+5)</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>SHANGHAI SHOUHUO RUBBER &amp; PLASTIC CO., LTD./ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>Mét</t>
         </is>
       </c>
-      <c r="E95" s="6" t="n">
+      <c r="G95" s="7" t="n">
         <v>494</v>
       </c>
-      <c r="F95" s="6" t="n">
+      <c r="H95" s="7" t="n">
         <v>5500000</v>
       </c>
-      <c r="G95" s="6" t="n">
+      <c r="I95" s="7" t="n">
         <v>2717000000</v>
       </c>
-      <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="7" t="inlineStr"/>
-      <c r="J95" s="6" t="n">
+      <c r="J95" s="6" t="inlineStr"/>
+      <c r="K95" s="6" t="inlineStr"/>
+      <c r="L95" s="7" t="n">
         <v>5500000</v>
       </c>
-      <c r="K95" s="6" t="n">
+      <c r="M95" s="7" t="n">
         <v>2717000000</v>
       </c>
-      <c r="L95" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" s="7" t="inlineStr"/>
+      <c r="N95" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="6" t="inlineStr"/>
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>5.08.78.858.CHN.00.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Không có trong KHSXKD 2026</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
@@ -4632,37 +6181,52 @@
           <t>3.70.75.350.CHN.00.000</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
-        <is>
-          <t>Cao su non áp cáp, Mã: 5380611; KT: 500x16400x1mm (10kg/cuộn) - Cao su non áp cáp, Mã: 5380611; KT: 500x16400x1mm (10kg/cuộn)</t>
-        </is>
-      </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Cao su non áp cáp, Mã: 5380611; KT: 500x16400x1mm (10kg/cuộn)</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>Cao su non áp cáp, Mã: 5380611; KT: 500x16400x1mm (10kg/cuộn)</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
+        <is>
+          <t>Rema Tiptop/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
         <is>
           <t>Cuộn</t>
         </is>
       </c>
-      <c r="E96" s="6" t="n">
+      <c r="G96" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="F96" s="6" t="n">
+      <c r="H96" s="7" t="n">
         <v>8200000</v>
       </c>
-      <c r="G96" s="6" t="n">
+      <c r="I96" s="7" t="n">
         <v>32800000</v>
       </c>
-      <c r="H96" s="7" t="inlineStr"/>
-      <c r="I96" s="7" t="inlineStr"/>
-      <c r="J96" s="6" t="n">
+      <c r="J96" s="6" t="inlineStr"/>
+      <c r="K96" s="6" t="inlineStr"/>
+      <c r="L96" s="7" t="n">
         <v>8200000</v>
       </c>
-      <c r="K96" s="6" t="n">
+      <c r="M96" s="7" t="n">
         <v>32800000</v>
       </c>
-      <c r="L96" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M96" s="7" t="inlineStr"/>
+      <c r="N96" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="6" t="inlineStr"/>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>3.70.75.350.CHN.00.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Có trong KHSXKD 2026. Kế hoạch sửa chữa các tuyến băng tải lõi thép dự kiến số vật tư mua sắm mới đang tồn kho. Cần mua sắm bổ sung.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n">
@@ -4673,37 +6237,52 @@
           <t>3.70.75.351.CHN.99.000</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn - Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Cao su non chèn cáp, Mã: 5440063; KT: 2.5x8x6800mm, hộp 2kg/12 cuộn</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
+        <is>
+          <t>Rema Tiptop/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>Hộp</t>
         </is>
       </c>
-      <c r="E97" s="6" t="n">
+      <c r="G97" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="F97" s="6" t="n">
+      <c r="H97" s="7" t="n">
         <v>3000000</v>
       </c>
-      <c r="G97" s="6" t="n">
+      <c r="I97" s="7" t="n">
         <v>48000000</v>
       </c>
-      <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="7" t="inlineStr"/>
-      <c r="J97" s="6" t="n">
+      <c r="J97" s="6" t="inlineStr"/>
+      <c r="K97" s="6" t="inlineStr"/>
+      <c r="L97" s="7" t="n">
         <v>3000000</v>
       </c>
-      <c r="K97" s="6" t="n">
+      <c r="M97" s="7" t="n">
         <v>48000000</v>
       </c>
-      <c r="L97" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="7" t="inlineStr"/>
+      <c r="N97" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="6" t="inlineStr"/>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>3.70.75.351.CHN.99.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Có trong KHSXKD 2026. Kế hoạch sửa chữa các tuyến băng tải lõi thép dự kiến số vật tư mua sắm mới đang tồn kho. Cần mua sắm bổ sung.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -4714,37 +6293,52 @@
           <t>3.70.75.349.CHN.99.000</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
-        <is>
-          <t>Cao su non, KT: B500x6x2800mm - Cao su non, KT: B500x6x2800mm</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Cao su non, KT: B500x6x2800mm</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Cao su non, KT: B500x6x2800mm</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>Rema Tiptop/ Đức</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
         <is>
           <t>Cuộn</t>
         </is>
       </c>
-      <c r="E98" s="6" t="n">
+      <c r="G98" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="F98" s="6" t="n">
+      <c r="H98" s="7" t="n">
         <v>6200000</v>
       </c>
-      <c r="G98" s="6" t="n">
+      <c r="I98" s="7" t="n">
         <v>124000000</v>
       </c>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="7" t="inlineStr"/>
-      <c r="J98" s="6" t="n">
+      <c r="J98" s="6" t="inlineStr"/>
+      <c r="K98" s="6" t="inlineStr"/>
+      <c r="L98" s="7" t="n">
         <v>6200000</v>
       </c>
-      <c r="K98" s="6" t="n">
+      <c r="M98" s="7" t="n">
         <v>124000000</v>
       </c>
-      <c r="L98" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="7" t="inlineStr"/>
+      <c r="N98" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" s="6" t="inlineStr"/>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>3.70.75.349.CHN.99.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Có trong KHSXKD 2026. Kế hoạch sửa chữa các tuyến băng tải lõi thép dự kiến số vật tư mua sắm mới đang tồn kho. Cần mua sắm bổ sung.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="n">
@@ -4755,37 +6349,52 @@
           <t>4.20.53.173.ESP.00.000</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Giấy chống dính, B1200 x 5m - Giấy chống dính, B1200 x 5m</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Giấy chống dính, B1200 x 5m</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Giấy chống dính, B1200 x 5m</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>Rema Tiptop/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
         <is>
           <t>Cuộn</t>
         </is>
       </c>
-      <c r="E99" s="6" t="n">
+      <c r="G99" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="F99" s="6" t="n">
+      <c r="H99" s="7" t="n">
         <v>1200000</v>
       </c>
-      <c r="G99" s="6" t="n">
+      <c r="I99" s="7" t="n">
         <v>9600000</v>
       </c>
-      <c r="H99" s="7" t="inlineStr"/>
-      <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="6" t="n">
+      <c r="J99" s="6" t="inlineStr"/>
+      <c r="K99" s="6" t="inlineStr"/>
+      <c r="L99" s="7" t="n">
         <v>1200000</v>
       </c>
-      <c r="K99" s="6" t="n">
+      <c r="M99" s="7" t="n">
         <v>9600000</v>
       </c>
-      <c r="L99" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="7" t="inlineStr"/>
+      <c r="N99" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" s="6" t="inlineStr"/>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>4.20.53.173.ESP.00.000 | Sửa chữa theo BBKT 324/2026/NL-VT4 | Có trong KHSXKD 2026 và đã mua sắm nhập kho. Kế hoạch sửa chữa các tuyến băng tải lõi thép dự kiến sử dụng hết số vật tư này. Cần mua sắm bổ sung.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n">
@@ -4796,9 +6405,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
-        <is>
-          <t>Cụm máy nén khí cho hệ thống chữa cháy Tuabine (Bao gồm cả động cơ)- Oil Less Air Compressor For Sprinkler System - Cụm máy nén khí cho hệ thống chữa cháy (Bao gồm cả động cơ)- Oil Less Air Compressor For Sprinkler System
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Cụm máy nén khí cho hệ thống chữa cháy Tuabine (Bao gồm cả động cơ)- Oil Less Air Compressor For Sprinkler System</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Cụm máy nén khí cho hệ thống chữa cháy (Bao gồm cả động cơ)- Oil Less Air Compressor For Sprinkler System
 Model: H1
 Part Number: 25835
 Công suất: 1/3 HP
@@ -4810,32 +6424,42 @@
 Nhà SX: Viking</t>
         </is>
       </c>
-      <c r="D100" s="4" t="inlineStr">
+      <c r="E100" s="5" t="inlineStr">
+        <is>
+          <t>Viking/ USA</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E100" s="6" t="n">
+      <c r="G100" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F100" s="6" t="n">
+      <c r="H100" s="7" t="n">
+        <v>338000000</v>
+      </c>
+      <c r="I100" s="7" t="n">
+        <v>676000000</v>
+      </c>
+      <c r="J100" s="6" t="inlineStr"/>
+      <c r="K100" s="6" t="inlineStr"/>
+      <c r="L100" s="7" t="n">
         <v>368000000</v>
       </c>
-      <c r="G100" s="6" t="n">
+      <c r="M100" s="7" t="n">
         <v>736000000</v>
       </c>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="7" t="inlineStr"/>
-      <c r="J100" s="6" t="n">
-        <v>368000000</v>
-      </c>
-      <c r="K100" s="6" t="n">
-        <v>736000000</v>
-      </c>
-      <c r="L100" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="7" t="inlineStr"/>
+      <c r="N100" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" s="6" t="inlineStr"/>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Thay thế cụm máy nén khí của hệ thống chữa cháy Tuabine S2 và S3 bị hư hỏng (bao gồm cả động cơ) theo BBKT 1722/2025, 1333/2026-VH-VT4 | Vật tư mua mới, không có trong KHSXKD năm 2026. Thông số kỹ thuật thay đổi so với BBKT do hãng ngừng sản xuất model cũ. Thông số kỹ thuật mới do hãng đề xuất theo Văn bản 3281/KHVT.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n">
@@ -4846,37 +6470,52 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Bản quyền Windows 11 Pro - Windows GGWA - Windows 11 Pro - Legalization Get Genuine</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Bản quyền Windows 11 Pro</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Windows GGWA - Windows 11 Pro - Legalization Get Genuine</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>Microsoft/ USA</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>License</t>
         </is>
       </c>
-      <c r="E101" s="6" t="n">
+      <c r="G101" s="7" t="n">
         <v>123</v>
       </c>
-      <c r="F101" s="6" t="n">
+      <c r="H101" s="7" t="n">
         <v>5300000</v>
       </c>
-      <c r="G101" s="6" t="n">
+      <c r="I101" s="7" t="n">
         <v>651900000</v>
       </c>
-      <c r="H101" s="7" t="inlineStr"/>
-      <c r="I101" s="7" t="inlineStr"/>
-      <c r="J101" s="6" t="n">
+      <c r="J101" s="6" t="inlineStr"/>
+      <c r="K101" s="6" t="inlineStr"/>
+      <c r="L101" s="7" t="n">
         <v>5300000</v>
       </c>
-      <c r="K101" s="6" t="n">
+      <c r="M101" s="7" t="n">
         <v>651900000</v>
       </c>
-      <c r="L101" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="7" t="inlineStr"/>
+      <c r="N101" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" s="6" t="inlineStr"/>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Theo Ttr số 3073/KTAT ngày 30/7/2026 | Windows MAK (Multiple Activation Key)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n">
@@ -4887,9 +6526,14 @@
           <t>Chưa có mã vật tư</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
-        <is>
-          <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW - Bơm (SP-Circulation pump): 
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Bơm (SP-Circulation pump):
 TP400 PP, P4-400V/50
 Động cơ bơm: type: FCA 112 MC-2/PHE, Công Suất : 5,5kW
 Điện áp: 400Vac
@@ -4904,32 +6548,860 @@
 IEC60034-1</t>
         </is>
       </c>
-      <c r="D102" s="4" t="inlineStr">
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>Grundfos/ Eu</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
         <is>
           <t>Bộ</t>
         </is>
       </c>
-      <c r="E102" s="6" t="n">
+      <c r="G102" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="F102" s="6" t="n">
+      <c r="H102" s="7" t="n">
         <v>770000000</v>
       </c>
-      <c r="G102" s="6" t="n">
+      <c r="I102" s="7" t="n">
         <v>1540000000</v>
       </c>
-      <c r="H102" s="7" t="inlineStr"/>
-      <c r="I102" s="7" t="inlineStr"/>
-      <c r="J102" s="6" t="n">
-        <v>770000000</v>
-      </c>
-      <c r="K102" s="6" t="n">
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 750.000.000 đ/Cái (08-27-26. BV-VT 4. . 1.620.000.000 vnd. 3 trang. R1.)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL Kế toán ERP của NMNĐ Vĩnh Tân 4.
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [TP400 PP], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 750.000.000 đ/Bộ.</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr"/>
+      <c r="L102" s="7" t="n">
+        <v>750000000</v>
+      </c>
+      <c r="M102" s="7" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="N102" s="7" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="O102" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Đàm phán giảm giá / Báo giá chào</t>
+        </is>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư | Khắc phục hư hỏng  theo BBKT491/2025, 859/2024, 819/2026/VH-VT4  | Thay thế cho vật tư có mã kế hoạch TXBS.26.1866 trong TTr 27/KTAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>99</v>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>2.05.01.029.VIE.00.000</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Phôi thép rèn, kích thước 40x65x150mm, vật liệu: ASTM A182 F91</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Phôi thép rèn; kích thước 40x65x150mm (dày x rộng x dài); Vật liệu: ASTM A182 F91; Phôi phải có đầy đủ hồ sơ/chứng chỉ chất lượng vật liệu, đảm bảo truy xuất được nguồn gốc vật liệu, đồng thời chứng minh đầy đủ các chỉ tiêu thành phần hóa học, cơ tính và các yêu cầu chất lượng liên quan đáp ứng yêu cầu của ASTM A182 F91</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>Baosteel/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H103" s="7" t="n">
+        <v>28700000</v>
+      </c>
+      <c r="I103" s="7" t="n">
+        <v>631400000</v>
+      </c>
+      <c r="J103" s="6" t="inlineStr"/>
+      <c r="K103" s="6" t="inlineStr"/>
+      <c r="L103" s="7" t="n">
+        <v>28700000</v>
+      </c>
+      <c r="M103" s="7" t="n">
+        <v>631400000</v>
+      </c>
+      <c r="N103" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="6" t="inlineStr"/>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>2.05.01.029.VIE.00.000 | Vật tư dùng để gia công thanh gia cường tầng cánh IP 18 theo Văn bản khuyến cáo số LTR-GMI-XVV4-0027 Rev.1 của Toshiba | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>2.05.01.030.VIE.00.000</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Phôi thép rèn, kích thước 35x45x175mm, vật liệu: ASTM A182 F91</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Phôi thép rèn; kích thước 35x45x175mm (dày x rộng x dài); Vật liệu: ASTM A182 F91; Phôi phải có đầy đủ hồ sơ/chứng chỉ chất lượng vật liệu, đảm bảo truy xuất được nguồn gốc vật liệu, đồng thời chứng minh đầy đủ các chỉ tiêu thành phần hóa học, cơ tính và các yêu cầu chất lượng liên quan đáp ứng yêu cầu của ASTM A182 F91</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>Baosteel/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>22</v>
+      </c>
+      <c r="H104" s="7" t="n">
+        <v>28700000</v>
+      </c>
+      <c r="I104" s="7" t="n">
+        <v>631400000</v>
+      </c>
+      <c r="J104" s="6" t="inlineStr"/>
+      <c r="K104" s="6" t="inlineStr"/>
+      <c r="L104" s="7" t="n">
+        <v>28700000</v>
+      </c>
+      <c r="M104" s="7" t="n">
+        <v>631400000</v>
+      </c>
+      <c r="N104" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="6" t="inlineStr"/>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>2.05.01.030.VIE.00.000 | Vật tư dùng để gia công thanh gia cường tầng cánh IP 20 theo Văn bản khuyến cáo số LTR-GMI-XVV4-0027 Rev.1 của Toshiba | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>4.31.28.586.JPN.99.000</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Que hàn TIG AWS A5.28 ER90S-B3Mn, loại 2.4mm; NSX: Kobelco/tương đương</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>Kiswel/ Hàn Quốc</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H105" s="7" t="n">
+        <v>725000</v>
+      </c>
+      <c r="I105" s="7" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="J105" s="6" t="inlineStr"/>
+      <c r="K105" s="6" t="inlineStr"/>
+      <c r="L105" s="7" t="n">
+        <v>725000</v>
+      </c>
+      <c r="M105" s="7" t="n">
+        <v>58000000</v>
+      </c>
+      <c r="N105" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O105" s="6" t="inlineStr"/>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>4.31.28.586.JPN.99.000 | Vật tư dùng để hàn thanh gia cường tầng cánh IP 18/20 theo Văn bản khuyến cáo số LTR-GMI-XVV4-0027 Rev.1 của Toshiba | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>102</v>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>Chưa có mã vật tư</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Phôi inconel 718, đường kính D50mm</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Phôi inconel 718, đường kính D50mm</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="inlineStr">
+        <is>
+          <t>Baosteel/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Mét</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="7" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="I106" s="7" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 750.000.000 đ/Cái (08-27-26. BV-VT 4. . 1.620.000.000 vnd. 3 trang. R1.)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL Kế toán ERP của NMNĐ Vĩnh Tân 4.
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [TP400 PP], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 750.000.000 đ/Bộ.</t>
+        </is>
+      </c>
+      <c r="K106" s="6" t="inlineStr"/>
+      <c r="L106" s="7" t="n">
+        <v>750000000</v>
+      </c>
+      <c r="M106" s="7" t="n">
+        <v>750000000</v>
+      </c>
+      <c r="N106" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="6" t="inlineStr"/>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>Chưa mua sắm | Mua sắm để gia công bulong tháo nửa dưới hộp chèn hơi số 2 theo Văn bản khuyến cáo số 3360/EPS-PXSCC-VT | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>103</v>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>5.33.85.051.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Phanh đuôi động cơ, model: BFK458-18E</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Model: BFK458-18E
+Size: 18
+Đường kính phủ bì: 218,6mm
+Lỗ lắp bulong: 6xM8
+Đường kính vòng chia bulong: 196mm
+Điện áp: 205VDC
+Nhà sản xuất: INTORQ</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>Intorq/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H107" s="7" t="n">
+        <v>63063000</v>
+      </c>
+      <c r="I107" s="7" t="n">
+        <v>126126000</v>
+      </c>
+      <c r="J107" s="6" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr"/>
+      <c r="L107" s="7" t="n">
+        <v>63063000</v>
+      </c>
+      <c r="M107" s="7" t="n">
+        <v>126126000</v>
+      </c>
+      <c r="N107" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="6" t="inlineStr"/>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>5.33.85.051.CHN.00.000 | Khắc phục phanh động cơ di chuyển MĐPĐ A,B bị hỏng theo BBKT 414/2026/NL-VT4, 415/2026/NL-VT4. |</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>104</v>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>3.84.64.021.GER.00.000</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Bộ chỉnh lưu model:169800, Ngõ vào: 220-440VAC, Ngõ ra: 110-205VDC</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>- Model:169800
+- Điện áp vào: 220-440VAC
+Điện áp ra: 110-205VDC</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>Siemens/ Đức</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H108" s="7" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="I108" s="7" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="J108" s="6" t="inlineStr"/>
+      <c r="K108" s="6" t="inlineStr"/>
+      <c r="L108" s="7" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="M108" s="7" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="N108" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="6" t="inlineStr"/>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>3.84.64.021.GER.00.000 | Khắc phục phanh động cơ di chuyển MĐPĐ A,B bị hỏng theo BBKT 414/2026/NL-VT4, 415/2026/NL-VT4. |</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>1.31.23.425.CHN.00.000</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Nhớt SHELL OMALA S4 WE 220</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Nhớt SHELL OMALA S4 WE 220; Độ nhớt ISO VG 220; Qui cách: 20l/xô; NSX: Shell/tương đương</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="inlineStr">
+        <is>
+          <t>Shell/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Lít</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H109" s="7" t="n">
+        <v>560000</v>
+      </c>
+      <c r="I109" s="7" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="J109" s="6" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr"/>
+      <c r="L109" s="7" t="n">
+        <v>560000</v>
+      </c>
+      <c r="M109" s="7" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="N109" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="6" t="inlineStr"/>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>1.31.23.425.CHN.00.000 | Vật tư dung để thay thế nhớt hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>106</v>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>4.88.65.314.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái), o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho Debris Filter có dw GIX/2945</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Bộ vòng đệm tròn làm kín/ Gear Sealing O-Ring; vật liệu EPDM; gồm: o-ring part no 21336 (1 cái) , o-ring part no 21351 (1 cái), o-ring part no 21724 (1 cái); sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>Gea-Bgr/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H110" s="7" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="I110" s="7" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="J110" s="6" t="inlineStr"/>
+      <c r="K110" s="6" t="inlineStr"/>
+      <c r="L110" s="7" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="M110" s="7" t="n">
+        <v>6700000</v>
+      </c>
+      <c r="N110" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O110" s="6" t="inlineStr"/>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>4.88.65.314.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>107</v>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>5.04.01.308.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>U-Seal part no: 21338 sử dụng cho bộ Debris Filter có dw GIX/2945 size DN2550</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>U-Seal part no: 21338; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>Gea-Bgr/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H111" s="7" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="I111" s="7" t="n">
+        <v>14600000</v>
+      </c>
+      <c r="J111" s="6" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr"/>
+      <c r="L111" s="7" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="M111" s="7" t="n">
+        <v>14600000</v>
+      </c>
+      <c r="N111" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="6" t="inlineStr"/>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>5.04.01.308.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>108</v>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>4.88.67.084.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho Debris Filter có dw GIX/2945</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Phớt chặn dầu/ Shaft Seal, Part no: 21340, sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="inlineStr">
+        <is>
+          <t>Gea-Bgr/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H112" s="7" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="I112" s="7" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="J112" s="6" t="inlineStr"/>
+      <c r="K112" s="6" t="inlineStr"/>
+      <c r="L112" s="7" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="M112" s="7" t="n">
+        <v>15800000</v>
+      </c>
+      <c r="N112" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="6" t="inlineStr"/>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>4.88.67.084.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>109</v>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>5.04.01.334.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Vòng đệm làm kín/ Gear Sealing Rear Bearing Part no: 21332, 21365 sử dụng cho Debris Filter có dw GIX/2945</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Vòng đệm làm kín/ Gear Sealing Rear Bearing Part no: 21332, 21365; vật liệu: A890 Gr CD4MCU &amp; POLYACE C; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Gea-Bgr/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Bộ</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" s="7" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="I113" s="7" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="J113" s="6" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr"/>
+      <c r="L113" s="7" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="M113" s="7" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="N113" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="6" t="inlineStr"/>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>5.04.01.334.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>5.04.01.316.IND.00.000</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>Vòng đệm tròn làm kín/ Gear Sealing Center Bolt Washer Part no: 21367 sử dụng cho Debris Filter có dw GIX/2945</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Vòng đệm tròn làm kín/ Gear Sealing Center Bolt Washer (Bush, vật liệu Nylon, AWC665), Part no: 21367; sử dụng cho bộ lọc Debris Filter có dw GIX/2945 size DN2550; NSX: GEA-BRG/tương đương</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Gea-Bgr/ Trung Quốc</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Cái</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" s="7" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="I114" s="7" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="J114" s="6" t="inlineStr"/>
+      <c r="K114" s="6" t="inlineStr"/>
+      <c r="L114" s="7" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="M114" s="7" t="n">
+        <v>8200000</v>
+      </c>
+      <c r="N114" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="6" t="inlineStr"/>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>5.04.01.316.IND.00.000 | Vật tư dùng để làm kín hộp giảm tốc của bộ lọc Debris Filter B tổ máy S1 theo BBKT số 1237/2026/VH-VT4 | Vật tư được đặt tên theo nguyên tắc chuẩn hoáVật tư không tồn kho, không có trong KHSXKD 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>111</v>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>5.30.10.355.VIE.99.000</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Gàu múc MĐPĐ, Thể tích: 0.75m3, Vật liệu: E355DD</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Thành Công/ Việt Nam</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H115" s="7" t="n">
+        <v>265000000</v>
+      </c>
+      <c r="I115" s="7" t="n">
+        <v>530000000</v>
+      </c>
+      <c r="J115" s="6" t="inlineStr"/>
+      <c r="K115" s="6" t="inlineStr"/>
+      <c r="L115" s="7" t="n">
+        <v>265000000</v>
+      </c>
+      <c r="M115" s="7" t="n">
+        <v>530000000</v>
+      </c>
+      <c r="N115" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O115" s="6" t="inlineStr"/>
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>5.30.10.355.VIE.99.000 | Mua bổ sung để duy trì dự phòng, đáp ứng dự phòng thay thế cho các MĐPĐ | STT số 91 theo Quyết định số 1274/QĐ-EVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>112</v>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>5.30.10.356.VIE.00.000</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>Gàu múc CSU</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>Thể tích 0,52 m3
+Vật liệu SMS570(JIS)+A709(ASTM)
+Bảng vẽ tham khảo</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Thành Công/ Việt Nam</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H116" s="7" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="I116" s="7" t="n">
         <v>1540000000</v>
       </c>
-      <c r="L102" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="7" t="inlineStr"/>
+      <c r="J116" s="6" t="inlineStr"/>
+      <c r="K116" s="6" t="inlineStr"/>
+      <c r="L116" s="7" t="n">
+        <v>140000000</v>
+      </c>
+      <c r="M116" s="7" t="n">
+        <v>1540000000</v>
+      </c>
+      <c r="N116" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O116" s="6" t="inlineStr"/>
+      <c r="P116" s="6" t="inlineStr">
+        <is>
+          <t>5.30.10.356.VIE.00.000 | Mua bổ sung để duy trì dự phòng, đáp ứng dự phòng thay thế cho các CSU | STT số 92 theo Quyết định số 1274/QĐ-EVN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/Bang_Tham_Dinh_Du_Toan.xlsx
+++ b/data/Bang_Tham_Dinh_Du_Toan.xlsx
@@ -500,7 +500,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Bang_Tham_Dinh_Du_Toan (3) - Bản Mới</t>
+          <t>Bang_Tham_Dinh_Du_Toan (3) - Bản Mới - Bản Mới</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,13 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>TỔ THẨM ĐỊNH NHÀ MÁY NHIỆT ĐIỆN VĨNH TÂN 4
-TỔ THẨM ĐỊNH DỰ TOÁN
-BÁO CÁO THUYẾT MINH THẨM ĐỊNH ĐƠN GIÁ VẬT TƯ
-Đơn vị yêu cầu: NMNĐ Vĩnh Tân 4
-Mã ERP: 3.82.63.134.ENG.00.000 | Số lượng: 4 Cái
-Tên vật tư: Module đầu vào input IUX 760 MI – Điện áp hoạt động: 17-28VDC
-Partno: 908531 | Hãng sản xuất: Minimax
-Đơn giá trình thẩm định: 13.559.000 đ/Cái
-1. TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
-Tổ Thẩm định tiến hành đối chiếu đơn giá trình thẩm định đối với mặt hàng Module đầu vào input IUX 760 MI (Partno: 908531, hãng Minimax) trên 5 cơ sở chứng cứ thu thập được, cụ thể:
-(1) Báo giá gốc thương mại; (2) Lịch sử mua sắm trên ERP Vĩnh Tân 4; (3) Cơ sở dữ liệu mua sắm EVN IMIS của các Đơn vị Phát điện trong Tập đoàn; (4) Cơ sở dữ liệu Mua sắm Công (e-GP); (5) Khảo sát giá thương mại điện tử trên các sàn giao dịch và Internet.
-Kết quả tổng hợp cho thấy đơn giá trình 13.559.000 đ/Cái là mức chào thấp nhất từ nhà thầu trong báo giá thương mại hiện tại; tuy nhiên khi đối chiếu với lị</t>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 13.559.000 đ/Cái (DTL 19.8.2026. xlsx)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 6.015.000 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 115/2023. Ttr 2562/KHVT) theo hóa đơn số 00000041. 42. 43. 44. 45. 46 ngày 30.08.2024 ngày 2024-10-31. SL: 117 Cái); Các đợt nhập khác: 17.670.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [908531], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Module đầu vào input IUX 760 MI] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 6.015.000 đ/Cái.</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr"/>
@@ -710,8 +705,13 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Ý KIẾN ĐÁNH GIÁ &amp; BẢN THUYẾT MINH THẨM ĐỊNH CỦA TỔ THẨM ĐỊNH DỰ TOÁN
-Căn cứ tính chất kỹ thuật, thương hiệu sản xuất và chứng cứ thu thập tại 05 cơ sở thẩm định, Tổ Thẩm định dự toán – Nhà máy Nhiệt điện Vĩnh Tân 4 thống nhất nội dung đánh giá đối với vật tư: Nút nhấn khẩn cấp Discovery Manual Call Point, Part no: 58100-953, nguồn cấp 17 – 28VDC, cấp bảo vệ IP67, nhà sản xuất Apollo (Mã ERP: 3.34.40.024.ENG.00.000), số lượng 01 cái, đơn giá trình thẩm định 14.208.000 đ</t>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 14.208.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 7.000.000 đ/Cái (HĐ: Nhập kho vật tư (QĐ:161) theo hóa đơn số 0000221 ngày 26.03.2021 ngày 2021-04-14. SL: 1 Cái)
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [58100-953], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Nút nhấn khẩn cấp - Discovery manual call point, Part no: 58100-953] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 7.000.000 đ/Cái.</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr"/>
@@ -863,7 +863,7 @@
         <is>
           <t># THUYẾT MINH THẨM ĐỊNH MỤC STT 4
 ## TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC
-Tổ Thẩm định thực hiện thẩm định đánh giá sau cùng đối với vật tư Solenoid van 600250-70900533 (Hãng SX: Bray International, số lượng 5 Bộ). Đơn giá dự toán trình là 64.000.000 đ/Bộ, cao hơn +610.4% so với đơn giá tham chiếu thấp nhất hợp lệ (9.009.300 đ từ Cơ sở 5). Tổ Thẩm định đề xuất điều chỉnh đơn giá theo giá thị trường quốc tế đã tính đủ chi phí nhập cảnh &amp; vận chuyển DDP Vĩ</t>
+Tổ Thẩm định thự</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr"/>
@@ -933,7 +933,7 @@
 • Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
 CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
 - Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.500.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 1 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
-- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL Kế toán ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Spiral Wound Gasket DN200 PN40], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Spiral Wound Gasket DN200 PN40], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
 - Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Spiral Wound Gasket DN200 PN40] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
 - Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [Spiral Wound Gasket] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
 - Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Spiral Wound Gasket DN200 PN40] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
@@ -1236,9 +1236,11 @@
 • Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
 CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
 - Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 1.315.000 VNĐ/Cái từ CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG (Trang 2 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
-- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL Kế toán ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Elbow union], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Elbow union], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
 - Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [10-PL A3C] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
-- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [W 10-PL A3C] trên Cổng Mạng Đấu thầu Quố</t>
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [W 10-PL A3C] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); kết quả đã rà soát e-GP: vật tư đặc thù, không ghi nhận gói thầu mua sắm tương đồng.
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [10-PL A3C] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 1.315.000 VNĐ/Cái.</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr"/>
@@ -1329,7 +1331,7 @@
 Đơn giá trình thẩm định 1.508.000 đ/Cái cao hơn **+80,2%** so với đơn giá tham chiếu thấp nhất hợp lệ là 836.800 đ/Cái (mức chênh tuyệt đối 671.200 đ/Cái). Với đặc tính kỹ thuật của cụm vật tư chuyên dụng G7, biên độ chênh lệch này vượt khá xa ngưỡng biến động hợp lý thường gặp (thông thường dưới 15–20%) giữa các báo giá cùng chủng loại, cùng xuất xứ. Tổ Thẩm định nhận thấy mức giá trình chưa có cơ sở thuyết phục để chứng minh tính hợp lý và cần được đàm phán điều chỉnh về mặt bằng giá thị trường.
 **3. Đối chiếu 05 cơ sở chứng cứ thẩm định**
 - **Cơ sở 1 – Báo giá gốc (thương mại):** Tổ Thẩm định đã đối chiếu các báo giá thương mại thu thập được; mức chào thấp nhất hợp lệ là **836.800 đ/Cái** từ Nhà thầu chào giá cạnh tranh. Đơn giá trình 1.508.000 đ/Cái không phải mức thấp nhất trên thị trường, chênh lệch +80,2% cho thấy dấu hiệu bất thường cần đàm phán.
-- **Cơ sở 2 – Cơ sở dữ liệu ERP Nhà máy Nhiệt điện Vĩnh Tân 4:** Qua rà soát CSDL Kế toán ERP, không có kết quả tra cứu nào có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Tổ Thẩm định **không áp dụng** CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- **Cơ sở 2 – Cơ sở dữ liệu ERP Nhà máy Nhiệt điện Vĩnh Tân 4:** Qua rà soát CSDL lịch sử mua sắm ERP, không có kết quả tra cứu nào có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Tổ Thẩm định **không áp dụng** CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
 - **Cơ sở 3 – Cơ sở dữ liệu EVN IMIS:** Tra cứu theo từ khóa **[DPR 10-L/S]** cho thấy các kết quả tìm thấy không tương đồng về quy cách/chủng loại với vật tư dự toán. Tổ Thẩm định **không áp dụng** làm căn cứ thẩm định.
 - **Cơ sở 4 – Hệ thống Mua sắm Công (e-GP) – muasamcong.mpi.gov.vn:** Tra cứu từ khóa **[126091]** tại thời điểm 18:31 ngày 07/09/2026 **chưa ghi nhận** kết quả trúng thầu tương tự. Tổ Thẩm định ghi nhận sự hạn chế dữ liệu tham chiếu từ kênh này.
 - **Cơ sở 5 – Thương mại điện tử:** Dữ liệu không khả dụng/không có kết quả phù hợp để đối chiếu; Tổ Thẩm định **không áp dụng** làm căn cứ so sánh đơn giá.
@@ -1407,13 +1409,23 @@
       <c r="I15" s="7" t="n">
         <v>24100000</v>
       </c>
-      <c r="J15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Chưa nạp dữ liệu Báo giá gốc
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 64.001.100 đ/Mét (HĐ: Nhập kho vật tư (HĐ: 40/2025) theo hóa đơn số 1956 ngày 30.10.2025 ngày 2025-12-12. SL: 3 Mét); Các đợt nhập khác: 16.649.700 đ, 11.181.019 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [B-210-2394], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Ống B-210-2394/1] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 64.001.100 đ/Mét.</t>
+        </is>
+      </c>
       <c r="K15" s="6" t="inlineStr"/>
       <c r="L15" s="7" t="n">
-        <v>1205000</v>
+        <v>64001100</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>24100000</v>
+        <v>1280022000</v>
       </c>
       <c r="N15" s="7" t="n">
         <v>0</v>
@@ -1479,18 +1491,32 @@
       <c r="I16" s="7" t="n">
         <v>117600000</v>
       </c>
-      <c r="J16" s="6" t="inlineStr"/>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 117.600.000 đ/Cái (CÔNG TY CỔ PHẦN XÂY DỰNG VÀ KỸ THUẬT THĂNG LONG)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 57.465.833 đ/Cái (HĐ: Nhập kho vật tư (HĐ: 65/2024) theo hóa đơn số 00000008 ngày 05.06.2025 ngày 2025-07-03. SL: 2 Cái); Các đợt nhập khác: 169.000.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [RTNC3], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Cảm biến đo khối lượng (Loadcell), model: RTNC3/10T] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾ</t>
+        </is>
+      </c>
       <c r="K16" s="6" t="inlineStr"/>
       <c r="L16" s="7" t="n">
-        <v>117600000</v>
+        <v>113232916.5</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>117600000</v>
+        <v>113232916</v>
       </c>
       <c r="N16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6" t="inlineStr"/>
+        <v>4367084</v>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 2: ERP Vĩnh Tân 4</t>
+        </is>
+      </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
           <t>3.96.13.021.GER.00.000 | Thay thế 01 cảm biến đo khối lượng (Loadcell) bồn chứa khí CO2 – Tổ máy S3 bị hư hỏng | BBKT 510/2026/VH-VT4. Vật tư không có trong KH SXKD 2026.</t>
@@ -1910,7 +1936,21 @@
       <c r="I23" s="7" t="n">
         <v>675500000</v>
       </c>
-      <c r="J23" s="6" t="inlineStr"/>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m (Mã ERP: 2.46.35.037.CHN.00.000).
+• Đơn giá trình thẩm định: 19.300.000 VNĐ (Số lượng: 35 Cái).
+• Đánh giá Chứng cứ Thẩm định: Đạt 60/100 điểm (Hạng B - 3/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 85/100 điểm (🟡 Hợp Lý (Nằm trong biên độ giá trung bình thị trường)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 18.522.000 VNĐ/Cái từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 3 Báo giá); đơn giá chào đối chiếu thấp hơn 778.000 VNĐ/Cái so với đơn giá trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Tra cứu theo từ khóa [2.46.35.037.CHN.00.000] trong CSDL lịch sử mua sắm ERP nội bộ nhà máy Vĩnh Tân 4; ghi nhận đơn giá nhập kho gần nhất là 21.200.000 VNĐ/Cái theo HĐ Nhập kho vật tư (HĐ: 120/2024) theo hóa đơn số 00000008 ngày 13.01.2025 (ký ngày 2025-01-16 00:00:00, cách đây 20 tháng ~ 1.7 năm - quá 12 tháng, tốc độ tăng giá bình quân -5.4%/năm so với CPI ~5.0%/năm).
+- Cơ sở 3 (EVN IMIS): Chưa đối chiếu CSDL Hợp đồng mua sắm toàn ngành EVN IMIS.
+- Cơ sở 4 (Mua Sắm Công e-GP): Tra cứu theo từ khóa [SS-T6-S-065-20] trên Cổng Mạng Đấu thầu Quốc gia (muasamcong.mpi.gov.vn); ghi nhận đơn giá trúng thầu công khai tham chiếu là 27.390.000 VNĐ/Cái (Nhà thầu Swagelok).
+- Cơ sở 5 (Thương Mại Điện Tử): Tra cứu theo từ khóa [Ống khí nén/ tube, Model: SS-T6-S-065-20, OD: 3/8 inch, Length: 6m] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đề xuất duyệt đơn giá thẩm định thống nhất là 18.522.000 VNĐ/Cái. Tiết kiệm dự toán 27.230.000 VNĐ (-4.0%).</t>
+        </is>
+      </c>
       <c r="K23" s="6" t="inlineStr"/>
       <c r="L23" s="7" t="n">
         <v>18522000</v>
@@ -1921,7 +1961,11 @@
       <c r="N23" s="7" t="n">
         <v>27230000</v>
       </c>
-      <c r="O23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
+        </is>
+      </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
           <t>2.46.35.037.CHN.00.000 | Khu vực hoàn nguyên xử lý nước230/2026/PXH-VT4 | Không có trong KHSXKD 2026</t>
@@ -5642,16 +5686,26 @@
       <c r="I86" s="7" t="n">
         <v>5236608000</v>
       </c>
-      <c r="J86" s="6" t="inlineStr"/>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
+• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 1.300.000 đ/Bộ (CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU)
+• Cơ sở 2 (ERP Vĩnh Tân 4): Lịch sử nhập kho ERP Vĩnh Tân 4: 1.845.000.000 đ/Bộ (HĐ: Nhập kho vật tư (HĐ: 32/2025) theo hóa đơn số 00000181 ngày 26.11.2025 ngày 2025-12-04. SL: 3 Bộ); Các đợt nhập khác: 1.293.213.000 đ
+• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [Lining Plate (Compound Armour], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
+• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Lining Plate (Compound Armour Plate) Tấm lót thân máy nghiền than] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
+• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
+KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 1.300.000 đ/Bộ.</t>
+        </is>
+      </c>
       <c r="K86" s="6" t="inlineStr"/>
       <c r="L86" s="7" t="n">
-        <v>2618304000</v>
+        <v>1300000</v>
       </c>
       <c r="M86" s="7" t="n">
-        <v>5236608000</v>
+        <v>2600000</v>
       </c>
       <c r="N86" s="7" t="n">
-        <v>0</v>
+        <v>5234008000</v>
       </c>
       <c r="O86" s="6" t="inlineStr"/>
       <c r="P86" s="6" t="inlineStr">
@@ -6571,7 +6625,7 @@
         <is>
           <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
 • Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 750.000.000 đ/Cái (08-27-26. BV-VT 4. . 1.620.000.000 vnd. 3 trang. R1.)
-• Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL Kế toán ERP của NMNĐ Vĩnh Tân 4.
+• Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4.
 • Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [TP400 PP], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
 • Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
 • Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
@@ -6807,26 +6861,34 @@
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>TỔNG HỢP 5 CƠ SỞ CHỨNG CỨ (Đã rà soát nhanh):
-• Cơ sở 1 (Báo Giá Gốc): Báo giá chào thấp nhất: 750.000.000 đ/Cái (08-27-26. BV-VT 4. . 1.620.000.000 vnd. 3 trang. R1.)
-• Cơ sở 2 (ERP Vĩnh Tân 4): Vật tư chưa có lịch sử mua sắm/nhập kho trong CSDL Kế toán ERP của NMNĐ Vĩnh Tân 4.
-• Cơ sở 3 (EVN IMIS): Trong khoảng thời gian tra cứu từ ngày 01/01/2023 đến nay, qua đối chiếu CSDL EVN IMIS theo từ khóa [TP400 PP], vật tư chưa tìm thấy dữ liệu mua sắm tương đương trên CSDL EVN IMIS.
-• Cơ sở 4 (Mua Sắm Công e-GP): Đã tra cứu từ khóa [Động cơ và bơm NAOH, Type: TP400 PP, FCA 112 MC-2/HE, Công suất: 5,5kW] trên Mạng Đấu thầu Quốc gia nhưng chưa ghi nhận kết quả trúng thầu tương tự.
-• Cơ sở 5 (TMĐT &amp; Tham Khảo Web): Vật tư đặc thù - Yêu cầu báo giá riêng (Contact for Quote)
-KẾT LUẬN: Đơn giá tham chiếu mốc thấp nhất đề xuất là 750.000.000 đ/Bộ.</t>
+          <t>TỔNG HỢP ĐÁNH GIÁ THẨM ĐỊNH MỤC: Phôi inconel 718, đường kính D50mm (Mã ERP: Chưa có mã vật tư).
+• Đơn giá trình thẩm định: 90.000.000 VNĐ (Số lượng: 1 Mét).
+• Đánh giá Chứng cứ Thẩm định: Đạt 100/100 điểm (Hạng A - 5/5 cơ sở chứng cứ đã nạp).
+• Đánh giá Mức độ Hợp lý Đơn giá: 100/100 điểm (🟢 Rất Hợp Lý (Đơn giá trình &lt;= Giá thấp nhất công khai)).
+CƠ SỞ THẨM ĐỊNH THỐNG NHẤT 5 CƠ SỞ CHỨNG CỨ:
+- Cơ sở 1 (Báo Giá Gốc): Đã đối chiếu các báo giá thương mại cạnh tranh trong Hồ sơ trình; ghi nhận đơn giá chào thấp nhất là 90.000.000 VNĐ/Mét từ CÔNG TY TNHH THƯƠNG MẠI KỸ THUẬT NĂNG LƯỢNG AN HIẾU (Trang 2 Báo giá); đơn giá chào đối chiếu khớp 100% với đơn giá dự toán trình.
+- Cơ sở 2 (ERP Vĩnh Tân 4): Qua rà soát CSDL lịch sử mua sắm ERP của NMNĐ Vĩnh Tân 4 theo từ khóa [Phôi inconel 718], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL ERP làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 3 (EVN IMIS): Tra cứu theo từ khóa [Phôi inconel 718, đường kính D50mm] trên CSDL Hợp đồng mua sắm toàn ngành EVN IMIS (2023-2026); kết quả đã đối soát toàn CSDL EVN: 0 bản ghi phù hợp (không phát sinh mua sắm tương đương).
+- Cơ sở 4 (Mua Sắm Công e-GP): Qua rà soát Cổng Mạng Đấu thầu Quốc gia e-GP (muasamcong.mpi.gov.vn) theo từ khóa [Phôi inconel 718], các kết quả tra cứu không có tính chất kỹ thuật và quy cách tương đồng phù hợp với vật tư đang xét. Thẩm định viên không áp dụng CSDL Mua sắm công làm căn cứ so sánh đơn giá cho mục này.
+- Cơ sở 5 (Thương Mại Điện Tử): Đã tra cứu từ khóa [Phôi inconel 718, đường kính D50mm] trên các cổng Internet &amp; Sàn TMĐT (eBay, Misumi, Google Web); kết quả ghi nhận vật tư thuộc danh mục thiết bị đặc thù công nghiệp, các trang web/nhà cung cấp không niêm yết đơn giá thương mại công khai (yêu cầu gửi thư yêu cầu báo giá riêng - Contact for Quote).
+KẾT LUẬN THẨM ĐỊNH: Đơn giá trình phù hợp với mặt bằng giá thị trường. Đề xuất phê duyệt giữ nguyên đơn giá trình là 90.000.000 VNĐ/Mét.</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr"/>
       <c r="L106" s="7" t="n">
-        <v>750000000</v>
+        <v>90000000</v>
       </c>
       <c r="M106" s="7" t="n">
-        <v>750000000</v>
+        <v>90000000</v>
       </c>
       <c r="N106" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O106" s="6" t="inlineStr"/>
+      <c r="O106" s="6" t="inlineStr">
+        <is>
+          <t>Cơ sở 1: Báo giá nộp kèm</t>
+        </is>
+      </c>
       <c r="P106" s="6" t="inlineStr">
         <is>
           <t>Chưa mua sắm | Mua sắm để gia công bulong tháo nửa dưới hộp chèn hơi số 2 theo Văn bản khuyến cáo số 3360/EPS-PXSCC-VT | Vật tư đặt tên theo nguyên tắc chuẩn hóa, không tồn khoVật tư không có trong KHSXKD năm 2026</t>
